--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -1,26 +1,158 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\ビジネスマネジャー検定\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546F7BFD-5261-48A4-A2E4-F6052D7E9E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="要点_問題" sheetId="1" r:id="rId1"/>
+    <sheet name="要点_解答" sheetId="2" r:id="rId2"/>
+    <sheet name="公式_問題_1" sheetId="3" r:id="rId3"/>
+    <sheet name="公式_問題_2" sheetId="5" r:id="rId4"/>
+    <sheet name="公式_問題_3" sheetId="6" r:id="rId5"/>
+    <sheet name="公式_分野別_問題" sheetId="9" r:id="rId6"/>
+    <sheet name="公式_解答_1" sheetId="4" r:id="rId7"/>
+    <sheet name="公式_解答_2" sheetId="7" r:id="rId8"/>
+    <sheet name="公式_解答_3" sheetId="8" r:id="rId9"/>
+    <sheet name="公式_分野別_解答" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="16">
+  <si>
+    <t>1 2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3 4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>✕</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 5 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t>○</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 5 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>○</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7　14</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -46,14 +178,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="パーセント" xfId="1" builtinId="5"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +475,3592 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:G10"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63EE4CF6-5FAF-4DA5-8DC2-19CF25D39295}">
+  <dimension ref="B2:C40"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="C10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="C12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="C27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="C28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29">
+        <v>22</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30">
+        <v>23</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32">
+        <v>25</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <v>26</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
+        <v>28</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <v>29</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37">
+        <v>30</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38">
+        <v>31</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012FFD73-E297-48A3-B6AA-5507307874C6}">
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="5" max="5" width="8.796875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2236A1BF-3EF1-45B2-8972-CB915DE2B880}">
+  <dimension ref="B2:H47"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46151</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25">
+        <v>7</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26">
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29">
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31">
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32">
+        <v>26</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33">
+        <v>27</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34">
+        <v>28</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35">
+        <v>29</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36">
+        <v>30</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37">
+        <v>31</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39">
+        <v>33</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40">
+        <v>34</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41">
+        <v>35</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42">
+        <v>36</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43">
+        <v>37</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44">
+        <v>38</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45">
+        <v>39</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46">
+        <v>40</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="D47" s="5">
+        <f>COUNTIF(D2:D46,"○")/COUNTA(D2:D46)</f>
+        <v>0.57777777777777772</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93AD5C9-1ECA-423E-8B2D-666B3CE254BE}">
+  <dimension ref="B2:E44"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21">
+        <v>19</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34">
+        <v>31</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36">
+        <v>33</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37">
+        <v>34</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38">
+        <v>35</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39">
+        <v>36</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40">
+        <v>37</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41">
+        <v>38</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42">
+        <v>39</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43">
+        <v>40</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="D44" s="5">
+        <f>COUNTIF(D2:D43,"○")/COUNTA(D2:D43)</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE21359A-624F-4C05-BEF8-F84C6A18C92D}">
+  <dimension ref="B2:E48"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="C26">
+        <v>9</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29">
+        <v>25</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30">
+        <v>26</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31">
+        <v>27</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34">
+        <v>29</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35">
+        <v>30</v>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36">
+        <v>31</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="D37" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41">
+        <v>34</v>
+      </c>
+      <c r="C41">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42">
+        <v>35</v>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43">
+        <v>36</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44">
+        <v>37</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45">
+        <v>38</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46">
+        <v>39</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47">
+        <v>40</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="D48" s="5">
+        <f>COUNTIF(D2:D47,"○")/COUNTA(D2:D47)</f>
+        <v>0.60869565217391308</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B9646A-C796-46EE-A75B-3B73C86BBB02}">
+  <dimension ref="B2:E41"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="C28">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29">
+        <v>22</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30">
+        <v>23</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32">
+        <v>25</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33">
+        <v>26</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35">
+        <v>28</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36">
+        <v>29</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37">
+        <v>30</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38">
+        <v>31</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>5</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="D41" s="5">
+        <f>COUNTIF(D2:D40,"○")/COUNTA(D2:D40)</f>
+        <v>0.5641025641025641</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086BB6CF-01C1-4BF3-BA05-A563BD7AE114}">
+  <dimension ref="B2:C46"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="C4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="C5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26">
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="C27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="C28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29">
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31">
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32">
+        <v>26</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <v>27</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
+        <v>28</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
+        <v>29</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <v>30</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37">
+        <v>31</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
+        <v>33</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
+        <v>34</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41">
+        <v>35</v>
+      </c>
+      <c r="C41">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42">
+        <v>36</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43">
+        <v>37</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44">
+        <v>38</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45">
+        <v>39</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46">
+        <v>40</v>
+      </c>
+      <c r="C46">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A85306-807E-4BFC-AD03-5D9093B5FD87}">
+  <dimension ref="B2:C43"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21">
+        <v>19</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="C22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
+        <v>31</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <v>33</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37">
+        <v>34</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38">
+        <v>35</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
+        <v>36</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
+        <v>37</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41">
+        <v>38</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42">
+        <v>39</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43">
+        <v>40</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4308920F-4F49-4EA4-A901-EE38B83F4FDA}">
+  <dimension ref="B2:C47"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="C26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="C28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29">
+        <v>25</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30">
+        <v>26</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31">
+        <v>27</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
+        <v>29</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
+        <v>30</v>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <v>31</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="C37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="C38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41">
+        <v>34</v>
+      </c>
+      <c r="C41">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42">
+        <v>35</v>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43">
+        <v>36</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44">
+        <v>37</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45">
+        <v>38</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46">
+        <v>39</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47">
+        <v>40</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\ビジネスマネジャー検定\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546F7BFD-5261-48A4-A2E4-F6052D7E9E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93C19A9-0BA1-46BE-BA61-408DB7BC3200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="16">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -1008,7 +1008,7 @@
   <dimension ref="B2:H47"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1029,6 +1029,9 @@
       <c r="F2">
         <v>2</v>
       </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
       <c r="H2" s="2">
         <v>46159</v>
       </c>
@@ -1045,6 +1048,9 @@
       </c>
       <c r="F3">
         <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -1057,6 +1063,9 @@
       <c r="F4">
         <v>12</v>
       </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="2:8">
       <c r="C5">
@@ -1068,6 +1077,9 @@
       <c r="F5">
         <v>8</v>
       </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="2:8">
       <c r="C6">
@@ -1079,6 +1091,9 @@
       <c r="F6">
         <v>3</v>
       </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="2:8">
       <c r="B7">
@@ -1093,6 +1108,9 @@
       <c r="F7">
         <v>6</v>
       </c>
+      <c r="G7" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8">
@@ -1106,6 +1124,9 @@
       </c>
       <c r="F8">
         <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="2:8">
@@ -1121,6 +1142,9 @@
       <c r="F9">
         <v>2</v>
       </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10">
@@ -1135,6 +1159,9 @@
       <c r="F10">
         <v>6</v>
       </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="2:8">
       <c r="B11">
@@ -1149,6 +1176,9 @@
       <c r="F11">
         <v>3</v>
       </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12">
@@ -1163,6 +1193,9 @@
       <c r="F12">
         <v>2</v>
       </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13">
@@ -1177,6 +1210,9 @@
       <c r="F13">
         <v>2</v>
       </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14">
@@ -1191,6 +1227,9 @@
       <c r="F14">
         <v>2</v>
       </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15">
@@ -1205,6 +1244,9 @@
       <c r="F15">
         <v>1</v>
       </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16">
@@ -1219,8 +1261,11 @@
       <c r="F16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="2:6">
+      <c r="G16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
       <c r="B17">
         <v>13</v>
       </c>
@@ -1233,8 +1278,11 @@
       <c r="F17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="2:6">
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
       <c r="B18">
         <v>14</v>
       </c>
@@ -1247,8 +1295,11 @@
       <c r="F18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="2:6">
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
       <c r="B19">
         <v>15</v>
       </c>
@@ -1261,8 +1312,11 @@
       <c r="F19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
       <c r="B20">
         <v>16</v>
       </c>
@@ -1275,8 +1329,11 @@
       <c r="F20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="2:6">
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
       <c r="B21">
         <v>17</v>
       </c>
@@ -1289,8 +1346,11 @@
       <c r="F21">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="2:6">
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
       <c r="B22">
         <v>18</v>
       </c>
@@ -1303,8 +1363,11 @@
       <c r="F22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="2:6">
+      <c r="G22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
       <c r="B23">
         <v>19</v>
       </c>
@@ -1317,8 +1380,11 @@
       <c r="F23">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="2:6">
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
       <c r="B24">
         <v>20</v>
       </c>
@@ -1331,8 +1397,11 @@
       <c r="F24">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="2:6">
+      <c r="G24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
       <c r="B25">
         <v>21</v>
       </c>
@@ -1345,8 +1414,11 @@
       <c r="F25">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="2:6">
+      <c r="G25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
       <c r="B26">
         <v>22</v>
       </c>
@@ -1359,24 +1431,33 @@
       <c r="F26">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="2:6">
+      <c r="G26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
       <c r="D27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="2:6">
+      <c r="G27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
       <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F28">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="2:6">
+      <c r="G28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
       <c r="B29">
         <v>23</v>
       </c>
@@ -1389,8 +1470,11 @@
       <c r="F29">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="2:6">
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
       <c r="B30">
         <v>24</v>
       </c>
@@ -1403,8 +1487,14 @@
       <c r="E30" s="2">
         <v>46152</v>
       </c>
-    </row>
-    <row r="31" spans="2:6">
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
       <c r="B31">
         <v>25</v>
       </c>
@@ -1414,8 +1504,14 @@
       <c r="D31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="2:6">
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
       <c r="B32">
         <v>26</v>
       </c>
@@ -1425,8 +1521,14 @@
       <c r="D32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="2:4">
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
       <c r="B33">
         <v>27</v>
       </c>
@@ -1436,8 +1538,14 @@
       <c r="D33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="2:4">
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
       <c r="B34">
         <v>28</v>
       </c>
@@ -1447,8 +1555,14 @@
       <c r="D34" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="2:4">
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35">
         <v>29</v>
       </c>
@@ -1458,8 +1572,14 @@
       <c r="D35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="2:4">
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36">
         <v>30</v>
       </c>
@@ -1469,8 +1589,14 @@
       <c r="D36" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="2:4">
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
       <c r="B37">
         <v>31</v>
       </c>
@@ -1480,8 +1606,14 @@
       <c r="D37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="2:4">
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
       <c r="B38">
         <v>32</v>
       </c>
@@ -1491,8 +1623,14 @@
       <c r="D38" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="2:4">
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
       <c r="B39">
         <v>33</v>
       </c>
@@ -1502,8 +1640,14 @@
       <c r="D39" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="2:4">
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
       <c r="B40">
         <v>34</v>
       </c>
@@ -1513,8 +1657,14 @@
       <c r="D40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="2:4">
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
       <c r="B41">
         <v>35</v>
       </c>
@@ -1524,8 +1674,14 @@
       <c r="D41" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:4">
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
       <c r="B42">
         <v>36</v>
       </c>
@@ -1535,8 +1691,14 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="43" spans="2:4">
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
       <c r="B43">
         <v>37</v>
       </c>
@@ -1546,8 +1708,14 @@
       <c r="D43" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:4">
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
       <c r="B44">
         <v>38</v>
       </c>
@@ -1557,8 +1725,14 @@
       <c r="D44" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:4">
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
       <c r="B45">
         <v>39</v>
       </c>
@@ -1568,8 +1742,14 @@
       <c r="D45" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:4">
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
       <c r="B46">
         <v>40</v>
       </c>
@@ -1579,11 +1759,21 @@
       <c r="D46" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:4">
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
       <c r="D47" s="5">
         <f>COUNTIF(D2:D46,"○")/COUNTA(D2:D46)</f>
         <v>0.57777777777777772</v>
+      </c>
+      <c r="G47" s="5">
+        <f>COUNTIF(G2:G46,"○")/COUNTA(G2:G46)</f>
+        <v>0.75555555555555554</v>
       </c>
     </row>
   </sheetData>
@@ -3011,6 +3201,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086BB6CF-01C1-4BF3-BA05-A563BD7AE114}">
   <dimension ref="B2:C46"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="3" max="3" width="8.796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2">

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\ビジネスマネジャー検定\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93C19A9-0BA1-46BE-BA61-408DB7BC3200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D39930-6A44-45C4-AEDA-98B98CEEC6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="要点_問題" sheetId="1" r:id="rId1"/>
@@ -40,15 +40,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="20">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -119,6 +116,22 @@
   </si>
   <si>
     <t>7　14</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3 6 7</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -476,13 +489,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G10"/>
+  <dimension ref="B2:H16"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="3"/>
+    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:8">
       <c r="B2">
         <v>1</v>
       </c>
@@ -492,107 +506,185 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="3" spans="2:7">
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7">
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
+    <row r="3" spans="2:8">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
+    <row r="6" spans="2:8">
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
+    <row r="7" spans="2:8">
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" t="s">
+    <row r="8" spans="2:8">
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="D9">
+      <c r="G8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="E9">
         <v>5</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="D10">
+    <row r="10" spans="2:8">
+      <c r="E10">
         <v>6</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="E16">
+        <v>6</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -909,13 +1001,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012FFD73-E297-48A3-B6AA-5507307874C6}">
-  <dimension ref="B2:E10"/>
+  <dimension ref="B2:F16"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="8.796875" style="3"/>
+    <col min="6" max="6" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:6">
       <c r="B2">
         <v>1</v>
       </c>
@@ -925,75 +1017,132 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5">
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3" t="s">
+    <row r="4" spans="2:6">
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="2:6">
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
+    <row r="7" spans="2:6">
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="D9">
+    <row r="8" spans="2:6">
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="E9">
         <v>5</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
-      <c r="D10">
+    <row r="10" spans="2:6">
+      <c r="E10">
         <v>6</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="E16">
+        <v>6</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1008,9 +1157,9 @@
   <dimension ref="B2:H47"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -1779,6 +1928,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1787,7 +1937,7 @@
   <dimension ref="B2:E44"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
@@ -2266,7 +2416,7 @@
   <dimension ref="B2:E48"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
@@ -2768,7 +2918,7 @@
   <dimension ref="B2:E41"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
@@ -3202,7 +3352,7 @@
   <dimension ref="B2:C46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="8.796875" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D39930-6A44-45C4-AEDA-98B98CEEC6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47CC89B-DF09-4E10-AD88-FCACA3D47ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="36">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -132,6 +132,70 @@
   </si>
   <si>
     <t>1 3 6 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 5 8 9 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4 5 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4 6 7 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5 8 9 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 4 6 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 5 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 5 8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 4 6</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -489,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H16"/>
+  <dimension ref="B2:H37"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="8.6640625" style="3"/>
@@ -688,9 +752,250 @@
         <v>4</v>
       </c>
     </row>
+    <row r="17" spans="4:8">
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="2">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8">
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8">
+      <c r="F19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8">
+      <c r="F20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8">
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="4:8">
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="4:8">
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="4:8">
+      <c r="E24">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="4:8">
+      <c r="E25">
+        <v>6</v>
+      </c>
+      <c r="F25" s="3">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="4:8">
+      <c r="E26">
+        <v>7</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="4:8">
+      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="4:8">
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="2">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="29" spans="4:8">
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="4:8">
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="4:8">
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="4:8">
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="4:8">
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="34" spans="4:8">
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="4:8">
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="4:8">
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="4:8">
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1001,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012FFD73-E297-48A3-B6AA-5507307874C6}">
-  <dimension ref="B2:F16"/>
+  <dimension ref="B2:F32"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="8.83203125" style="3"/>
@@ -1143,6 +1448,131 @@
       </c>
       <c r="F16" s="3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6">
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6">
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6">
+      <c r="F19" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6">
+      <c r="F20" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6">
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6">
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6">
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6">
+      <c r="E24">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6">
+      <c r="E25">
+        <v>6</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6">
+      <c r="E26">
+        <v>7</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6">
+      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6">
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="4:6">
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6">
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="4:6">
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6">
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47CC89B-DF09-4E10-AD88-FCACA3D47ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4491435F-0B6B-45CD-A8ED-CD087E8D5484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="59">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -196,6 +196,125 @@
   </si>
   <si>
     <t>2 4 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 5 8 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3 4 5 7 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3 4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SDGs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2030年</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーポレートガバナンス・コード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統治を意味するガバナンス</t>
+    <rPh sb="0" eb="2">
+      <t>トウチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>XRP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KPI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KGI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 4 6 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3 4 5 7 9 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ESG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スチュアートシップ・コード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境への配慮</t>
+    <rPh sb="0" eb="2">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人権などを意味するソーシャル</t>
+    <rPh sb="0" eb="2">
+      <t>ジンケン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 4 5</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -553,10 +672,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H37"/>
+  <dimension ref="B2:H66"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="6" max="6" width="8.6640625" style="3"/>
+    <col min="6" max="6" width="15" style="3" customWidth="1"/>
     <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -989,6 +1108,307 @@
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="4:8">
+      <c r="D38">
+        <v>6</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="4:8">
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="4:8">
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="4:8">
+      <c r="D41">
+        <v>7</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="2">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="42" spans="4:8">
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="4:8">
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="4:8">
+      <c r="F44" s="3">
+        <v>3</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="4:8">
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="4:8">
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="4:8">
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="4:8">
+      <c r="F48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8">
+      <c r="F49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8">
+      <c r="F50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8">
+      <c r="F51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H51" s="2">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8">
+      <c r="G52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="4:8">
+      <c r="G53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" spans="4:8">
+      <c r="G54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="4:8">
+      <c r="E55">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3">
+        <v>3</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8">
+      <c r="D56">
+        <v>8</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3">
+        <v>4</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H56" s="2">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8">
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8">
+      <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8">
+      <c r="E59">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8">
+      <c r="E60">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3">
+        <v>4</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8">
+      <c r="E61">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8">
+      <c r="F62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8">
+      <c r="E63">
+        <v>7</v>
+      </c>
+      <c r="F63" s="3">
+        <v>4</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8">
+      <c r="E64">
+        <v>8</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="5:7">
+      <c r="E65">
+        <v>9</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="5:7">
+      <c r="E66">
+        <v>10</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1306,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012FFD73-E297-48A3-B6AA-5507307874C6}">
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:F66"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="8.83203125" style="3"/>
@@ -1573,6 +1993,260 @@
       </c>
       <c r="F32" s="3" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6">
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="4:6">
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6">
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="4:6">
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="4:6">
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:6">
+      <c r="D38">
+        <v>6</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="4:6">
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="4:6">
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="4:6">
+      <c r="D41">
+        <v>7</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="4:6">
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="4:6">
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="4:6">
+      <c r="F44" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="4:6">
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="4:6">
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="4:6">
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="4:6">
+      <c r="F48" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="4:6">
+      <c r="F49" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="4:6">
+      <c r="F50" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="4:6">
+      <c r="F51" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="4:6">
+      <c r="F52" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="4:6">
+      <c r="F53" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="4:6">
+      <c r="F54" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="4:6">
+      <c r="E55">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="4:6">
+      <c r="D56">
+        <v>8</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="4:6">
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="4:6">
+      <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="4:6">
+      <c r="E59">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="4:6">
+      <c r="E60">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="4:6">
+      <c r="E61">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="4:6">
+      <c r="F62" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="4:6">
+      <c r="E63">
+        <v>7</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="4:6">
+      <c r="E64">
+        <v>8</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="5:6">
+      <c r="E65">
+        <v>9</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="5:6">
+      <c r="E66">
+        <v>10</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4491435F-0B6B-45CD-A8ED-CD087E8D5484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187E4E93-A398-4935-A295-34B750F1C7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="69">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -315,6 +315,61 @@
   </si>
   <si>
     <t>2 4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50 40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>40 80 100</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャッシュフロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>純利益</t>
+    <rPh sb="0" eb="3">
+      <t>ジュンリエキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>営業利益</t>
+    <rPh sb="0" eb="2">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リエキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 4 5 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4 5 6</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -672,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H66"/>
+  <dimension ref="B2:H86"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="15" style="3" customWidth="1"/>
@@ -1390,7 +1445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="5:7">
+    <row r="65" spans="4:7">
       <c r="E65">
         <v>9</v>
       </c>
@@ -1401,7 +1456,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="5:7">
+    <row r="66" spans="4:7">
       <c r="E66">
         <v>10</v>
       </c>
@@ -1410,6 +1465,214 @@
       </c>
       <c r="G66" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="4:7">
+      <c r="D67">
+        <v>9</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="4:7">
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="4:7">
+      <c r="E69">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="4:7">
+      <c r="E70">
+        <v>4</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="4:7">
+      <c r="E71">
+        <v>5</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="4:7">
+      <c r="G72" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="4:7">
+      <c r="F73" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="4:7">
+      <c r="F74" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="4:7">
+      <c r="F75" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="4:7">
+      <c r="F76" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="4:7">
+      <c r="E77">
+        <v>6</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="4:7">
+      <c r="E78">
+        <v>7</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="4:7">
+      <c r="E79">
+        <v>8</v>
+      </c>
+      <c r="F79" s="3">
+        <v>2</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="4:7">
+      <c r="E80">
+        <v>9</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="4:8">
+      <c r="E81">
+        <v>10</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="4:8">
+      <c r="D82">
+        <v>10</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H82" s="2">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="83" spans="4:8">
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="4:8">
+      <c r="E84">
+        <v>3</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="4:8">
+      <c r="E85">
+        <v>4</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="4:8">
+      <c r="E86">
+        <v>5</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187E4E93-A398-4935-A295-34B750F1C7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFC6D30-FA63-47DD-A22E-9E7DE83476A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="70">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -370,6 +370,19 @@
   </si>
   <si>
     <t>4 5 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>整理　整頓　清潔</t>
+    <rPh sb="0" eb="2">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイトン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイケツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -727,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H86"/>
+  <dimension ref="B2:H93"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="15" style="3" customWidth="1"/>
@@ -1672,6 +1685,86 @@
         <v>10</v>
       </c>
       <c r="G86" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="4:8">
+      <c r="D87">
+        <v>11</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="4:8">
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="4:8">
+      <c r="E89">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="4:8">
+      <c r="E90">
+        <v>4</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="4:8">
+      <c r="E91">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="4:8">
+      <c r="E92">
+        <v>6</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="4:8">
+      <c r="E93">
+        <v>7</v>
+      </c>
+      <c r="F93" s="3">
+        <v>2</v>
+      </c>
+      <c r="G93" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFC6D30-FA63-47DD-A22E-9E7DE83476A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6518446-C8C7-405F-A422-31E9F7AE2163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="72">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -383,6 +383,14 @@
     <rPh sb="6" eb="8">
       <t>セイケツ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3 5</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -740,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H93"/>
+  <dimension ref="B2:H105"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="15" style="3" customWidth="1"/>
@@ -1765,6 +1773,138 @@
         <v>2</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="4:8">
+      <c r="D94">
+        <v>12</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="4:8">
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="4:8">
+      <c r="E96">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3">
+        <v>4</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="5:7">
+      <c r="E97">
+        <v>4</v>
+      </c>
+      <c r="F97" s="3">
+        <v>3</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="5:7">
+      <c r="E98">
+        <v>5</v>
+      </c>
+      <c r="F98" s="3">
+        <v>3</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="5:7">
+      <c r="E99">
+        <v>6</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="5:7">
+      <c r="E100">
+        <v>7</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="5:7">
+      <c r="E101">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="5:7">
+      <c r="E102">
+        <v>9</v>
+      </c>
+      <c r="F102" s="3">
+        <v>1</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="5:7">
+      <c r="E103">
+        <v>10</v>
+      </c>
+      <c r="F103" s="3">
+        <v>5</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="5:7">
+      <c r="E104">
+        <v>11</v>
+      </c>
+      <c r="F104" s="3">
+        <v>3</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="5:7">
+      <c r="E105">
+        <v>12</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1B0DED-7F22-4868-8666-63C17C79B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B511E-91D6-4D94-9340-B5C906736529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="176">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -1016,6 +1016,14 @@
   </si>
   <si>
     <t>デジタルトランスフォーメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 5 6 8 9 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 4 5 9 10</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1081,7 +1089,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1090,13 +1098,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -1383,8 +1384,9 @@
   <dimension ref="B2:K189"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="6" max="6" width="15" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="3" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
@@ -1411,13 +1413,13 @@
       <c r="H2" s="2">
         <v>46139</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="8">
+      <c r="J2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="2">
         <v>46173</v>
       </c>
     </row>
@@ -1431,13 +1433,12 @@
       <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="6"/>
+      <c r="I3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="2:11">
       <c r="E4">
@@ -1449,13 +1450,12 @@
       <c r="G4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="6"/>
+      <c r="J4" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="2:11">
       <c r="C5">
@@ -1476,13 +1476,12 @@
       <c r="H5" s="2">
         <v>46139</v>
       </c>
-      <c r="I5" s="9">
-        <v>1</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="6"/>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="2:11">
       <c r="E6">
@@ -1494,13 +1493,12 @@
       <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="6"/>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="2:11">
       <c r="E7">
@@ -1512,13 +1510,12 @@
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="6"/>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="2:11">
       <c r="E8">
@@ -1530,13 +1527,12 @@
       <c r="G8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="6"/>
+      <c r="J8" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="2:11">
       <c r="E9">
@@ -1548,13 +1544,12 @@
       <c r="G9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="6"/>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="2:11">
       <c r="E10">
@@ -1566,13 +1561,12 @@
       <c r="G10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="6"/>
+      <c r="J10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="2:11">
       <c r="D11">
@@ -1590,13 +1584,12 @@
       <c r="H11" s="2">
         <v>46160</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K11" s="6"/>
+      <c r="J11" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="2:11">
       <c r="E12">
@@ -1608,13 +1601,12 @@
       <c r="G12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="9">
-        <v>4</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="6"/>
+      <c r="I12" s="3">
+        <v>4</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13" spans="2:11">
       <c r="E13">
@@ -1626,13 +1618,12 @@
       <c r="G13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="6"/>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" spans="2:11">
       <c r="E14">
@@ -1644,13 +1635,12 @@
       <c r="G14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="9">
-        <v>1</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="6"/>
+      <c r="I14" s="3">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="15" spans="2:11">
       <c r="E15">
@@ -1662,13 +1652,12 @@
       <c r="G15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="6"/>
+      <c r="J15" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="2:11">
       <c r="E16">
@@ -1680,13 +1669,12 @@
       <c r="G16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="9">
-        <v>4</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K16" s="6"/>
+      <c r="I16" s="3">
+        <v>4</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="4:11">
       <c r="D17">
@@ -1704,13 +1692,12 @@
       <c r="H17" s="2">
         <v>46161</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" s="6"/>
+      <c r="I17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="18" spans="4:11">
       <c r="E18">
@@ -1722,13 +1709,12 @@
       <c r="G18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" s="6"/>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" spans="4:11">
       <c r="F19" s="3" t="s">
@@ -1737,13 +1723,12 @@
       <c r="G19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="6"/>
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="20" spans="4:11">
       <c r="F20" s="3" t="s">
@@ -1752,13 +1737,12 @@
       <c r="G20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" s="6"/>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="21" spans="4:11">
       <c r="F21" s="3" t="s">
@@ -1767,13 +1751,12 @@
       <c r="G21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="6"/>
+      <c r="J21" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" spans="4:11">
       <c r="E22">
@@ -1785,13 +1768,12 @@
       <c r="G22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="6"/>
+      <c r="J22" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="4:11">
       <c r="E23">
@@ -1803,13 +1785,12 @@
       <c r="G23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I23" s="9">
-        <v>4</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="6"/>
+      <c r="I23" s="3">
+        <v>4</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="4:11">
       <c r="E24">
@@ -1821,13 +1802,12 @@
       <c r="G24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="9">
-        <v>3</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="6"/>
+      <c r="I24" s="3">
+        <v>3</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="25" spans="4:11">
       <c r="E25">
@@ -1839,13 +1819,12 @@
       <c r="G25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="9">
-        <v>4</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="6"/>
+      <c r="I25" s="3">
+        <v>4</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="4:11">
       <c r="E26">
@@ -1857,13 +1836,12 @@
       <c r="G26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J26" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="6"/>
+      <c r="J26" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="4:11">
       <c r="E27">
@@ -1875,13 +1853,12 @@
       <c r="G27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K27" s="6"/>
+      <c r="J27" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28">
@@ -1899,6 +1876,15 @@
       <c r="H28" s="2">
         <v>46162</v>
       </c>
+      <c r="I28" t="s">
+        <v>174</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K28" s="2">
+        <v>46174</v>
+      </c>
     </row>
     <row r="29" spans="4:11">
       <c r="E29">
@@ -1910,6 +1896,12 @@
       <c r="G29" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="4:11">
       <c r="E30">
@@ -1921,6 +1913,12 @@
       <c r="G30" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="4:11">
       <c r="E31">
@@ -1930,6 +1928,12 @@
         <v>28</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1943,6 +1947,12 @@
       <c r="G32" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="33" spans="4:8">
       <c r="D33">
@@ -2909,718 +2919,658 @@
       </c>
     </row>
     <row r="122" spans="2:8">
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6">
+      <c r="D122">
         <v>15</v>
       </c>
-      <c r="E122" s="6">
-        <v>1</v>
-      </c>
-      <c r="F122" s="9" t="s">
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G122" s="7" t="s">
+      <c r="G122" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H122" s="8">
+      <c r="H122" s="2">
         <v>46172</v>
       </c>
     </row>
     <row r="123" spans="2:8">
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6">
-        <v>2</v>
-      </c>
-      <c r="F123" s="9" t="s">
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G123" s="7" t="s">
+      <c r="G123" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H123" s="6"/>
     </row>
     <row r="124" spans="2:8">
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="6">
-        <v>3</v>
-      </c>
-      <c r="F124" s="9" t="s">
+      <c r="E124">
+        <v>3</v>
+      </c>
+      <c r="F124" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G124" s="7" t="s">
+      <c r="G124" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H124" s="6"/>
     </row>
     <row r="125" spans="2:8">
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6">
-        <v>4</v>
-      </c>
-      <c r="F125" s="9" t="s">
+      <c r="E125">
+        <v>4</v>
+      </c>
+      <c r="F125" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G125" s="6" t="s">
+      <c r="G125" t="s">
         <v>103</v>
       </c>
-      <c r="H125" s="6"/>
     </row>
     <row r="126" spans="2:8">
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6">
+      <c r="E126">
         <v>5</v>
       </c>
-      <c r="F126" s="9" t="s">
+      <c r="F126" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G126" s="7" t="s">
+      <c r="G126" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H126" s="6"/>
     </row>
     <row r="127" spans="2:8">
-      <c r="B127" s="6">
-        <v>2</v>
-      </c>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6">
-        <v>1</v>
-      </c>
-      <c r="F127" s="9" t="s">
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G127" s="6" t="s">
+      <c r="G127" t="s">
         <v>103</v>
       </c>
-      <c r="H127" s="6"/>
     </row>
     <row r="128" spans="2:8">
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6">
-        <v>2</v>
-      </c>
-      <c r="F128" s="9" t="s">
+      <c r="E128">
+        <v>2</v>
+      </c>
+      <c r="F128" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G128" s="6" t="s">
+      <c r="G128" t="s">
         <v>103</v>
       </c>
-      <c r="H128" s="6"/>
     </row>
     <row r="129" spans="5:7">
-      <c r="E129" s="6">
-        <v>3</v>
-      </c>
-      <c r="F129" s="9">
-        <v>1</v>
-      </c>
-      <c r="G129" s="7" t="s">
+      <c r="E129">
+        <v>3</v>
+      </c>
+      <c r="F129" s="3">
+        <v>1</v>
+      </c>
+      <c r="G129" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="130" spans="5:7">
-      <c r="E130" s="6">
-        <v>4</v>
-      </c>
-      <c r="F130" s="9" t="s">
+      <c r="E130">
+        <v>4</v>
+      </c>
+      <c r="F130" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G130" s="7" t="s">
+      <c r="G130" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="131" spans="5:7">
-      <c r="E131" s="6">
+      <c r="E131">
         <v>5</v>
       </c>
-      <c r="F131" s="9" t="s">
+      <c r="F131" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G131" s="7" t="s">
+      <c r="G131" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="132" spans="5:7">
-      <c r="E132" s="6">
+      <c r="E132">
         <v>6</v>
       </c>
-      <c r="F132" s="9" t="s">
+      <c r="F132" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G132" s="7" t="s">
+      <c r="G132" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="133" spans="5:7">
-      <c r="E133" s="6">
+      <c r="E133">
         <v>7</v>
       </c>
-      <c r="F133" s="9" t="s">
+      <c r="F133" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G133" s="7" t="s">
+      <c r="G133" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="134" spans="5:7">
-      <c r="E134" s="6">
+      <c r="E134">
         <v>8</v>
       </c>
-      <c r="F134" s="9">
-        <v>2</v>
-      </c>
-      <c r="G134" s="7" t="s">
+      <c r="F134" s="3">
+        <v>2</v>
+      </c>
+      <c r="G134" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="135" spans="5:7">
-      <c r="E135" s="6">
+      <c r="E135">
         <v>9</v>
       </c>
-      <c r="F135" s="9">
+      <c r="F135" s="3">
         <v>5</v>
       </c>
-      <c r="G135" s="7" t="s">
+      <c r="G135" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="136" spans="5:7">
-      <c r="E136" s="6">
+      <c r="E136">
         <v>10</v>
       </c>
-      <c r="F136" s="9" t="s">
+      <c r="F136" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G136" s="7" t="s">
+      <c r="G136" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="137" spans="5:7">
-      <c r="E137" s="6">
+      <c r="E137">
         <v>11</v>
       </c>
-      <c r="F137" s="9">
-        <v>4</v>
-      </c>
-      <c r="G137" s="6" t="s">
+      <c r="F137" s="3">
+        <v>4</v>
+      </c>
+      <c r="G137" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="138" spans="5:7">
-      <c r="E138" s="6">
+      <c r="E138">
         <v>12</v>
       </c>
-      <c r="F138" s="9" t="s">
+      <c r="F138" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G138" s="6" t="s">
+      <c r="G138" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="139" spans="5:7">
-      <c r="E139" s="6"/>
-      <c r="F139" s="9" t="s">
+      <c r="F139" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G139" s="6" t="s">
+      <c r="G139" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="140" spans="5:7">
-      <c r="E140" s="6"/>
-      <c r="F140" s="9" t="s">
+      <c r="F140" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G140" s="6" t="s">
+      <c r="G140" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="141" spans="5:7">
-      <c r="E141" s="6"/>
-      <c r="F141" s="9" t="s">
+      <c r="F141" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G141" s="6" t="s">
+      <c r="G141" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="142" spans="5:7">
-      <c r="E142" s="6"/>
-      <c r="F142" s="9" t="s">
+      <c r="F142" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G142" s="7" t="s">
+      <c r="G142" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="143" spans="5:7">
-      <c r="E143" s="6"/>
-      <c r="F143" s="9" t="s">
+      <c r="F143" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G143" s="6" t="s">
+      <c r="G143" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="144" spans="5:7">
-      <c r="E144" s="6">
+      <c r="E144">
         <v>13</v>
       </c>
-      <c r="F144" s="9" t="s">
+      <c r="F144" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G144" s="6" t="s">
+      <c r="G144" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="145" spans="5:7">
-      <c r="E145" s="6">
-        <v>14</v>
-      </c>
-      <c r="F145" s="9" t="s">
+      <c r="E145">
+        <v>14</v>
+      </c>
+      <c r="F145" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G145" s="6" t="s">
+      <c r="G145" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="146" spans="5:7">
-      <c r="E146" s="6"/>
-      <c r="F146" s="9" t="s">
+      <c r="F146" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G146" s="6" t="s">
+      <c r="G146" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="147" spans="5:7">
-      <c r="E147" s="6"/>
-      <c r="F147" s="9" t="s">
+      <c r="F147" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G147" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="148" spans="5:7">
-      <c r="E148" s="6"/>
-      <c r="F148" s="9" t="s">
+      <c r="F148" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="G148" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="149" spans="5:7">
-      <c r="E149" s="6"/>
-      <c r="F149" s="9" t="s">
+      <c r="F149" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G149" s="6" t="s">
+      <c r="G149" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="150" spans="5:7">
-      <c r="E150" s="6">
+      <c r="E150">
         <v>15</v>
       </c>
-      <c r="F150" s="9" t="s">
+      <c r="F150" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G150" s="7" t="s">
+      <c r="G150" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="151" spans="5:7">
-      <c r="E151" s="6"/>
-      <c r="F151" s="9" t="s">
+      <c r="F151" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G151" s="6" t="s">
+      <c r="G151" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="152" spans="5:7">
-      <c r="E152" s="6"/>
-      <c r="F152" s="9" t="s">
+      <c r="F152" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G152" s="6" t="s">
+      <c r="G152" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="153" spans="5:7">
-      <c r="E153" s="6"/>
-      <c r="F153" s="9" t="s">
+      <c r="F153" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G153" s="6" t="s">
+      <c r="G153" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="154" spans="5:7">
-      <c r="E154" s="6"/>
-      <c r="F154" s="9" t="s">
+      <c r="F154" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G154" s="6" t="s">
+      <c r="G154" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="155" spans="5:7">
-      <c r="E155" s="6"/>
-      <c r="F155" s="9" t="s">
+      <c r="F155" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G155" s="7" t="s">
+      <c r="G155" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="156" spans="5:7">
-      <c r="E156" s="6"/>
-      <c r="F156" s="9" t="s">
+      <c r="F156" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G156" s="6" t="s">
+      <c r="G156" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="157" spans="5:7">
-      <c r="E157" s="6">
+      <c r="E157">
         <v>16</v>
       </c>
-      <c r="F157" s="9" t="s">
+      <c r="F157" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G157" s="7" t="s">
+      <c r="G157" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="158" spans="5:7">
-      <c r="E158" s="6">
+      <c r="E158">
         <v>17</v>
       </c>
-      <c r="F158" s="9" t="s">
+      <c r="F158" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G158" s="7" t="s">
+      <c r="G158" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="159" spans="5:7">
-      <c r="E159" s="6">
+      <c r="E159">
         <v>18</v>
       </c>
-      <c r="F159" s="9" t="s">
+      <c r="F159" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G159" s="7" t="s">
+      <c r="G159" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="160" spans="5:7">
-      <c r="E160" s="6">
+      <c r="E160">
         <v>19</v>
       </c>
-      <c r="F160" s="9" t="s">
+      <c r="F160" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G160" s="6" t="s">
+      <c r="G160" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="161" spans="5:7">
-      <c r="E161" s="6">
+      <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="9" t="s">
+      <c r="F161" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G161" s="7" t="s">
+      <c r="G161" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="162" spans="5:7">
-      <c r="E162" s="6">
+      <c r="E162">
         <v>21</v>
       </c>
-      <c r="F162" s="9" t="s">
+      <c r="F162" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G162" s="7" t="s">
+      <c r="G162" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="163" spans="5:7">
-      <c r="E163" s="6">
+      <c r="E163">
         <v>22</v>
       </c>
-      <c r="F163" s="9" t="s">
+      <c r="F163" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="G163" s="6" t="s">
+      <c r="G163" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="164" spans="5:7">
-      <c r="E164" s="6">
+      <c r="E164">
         <v>23</v>
       </c>
-      <c r="F164" s="9">
+      <c r="F164" s="3">
         <v>6</v>
       </c>
-      <c r="G164" s="7" t="s">
+      <c r="G164" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="165" spans="5:7">
-      <c r="E165" s="6">
+      <c r="E165">
         <v>24</v>
       </c>
-      <c r="F165" s="9" t="s">
+      <c r="F165" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G165" s="7" t="s">
+      <c r="G165" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="166" spans="5:7">
-      <c r="E166" s="6">
+      <c r="E166">
         <v>25</v>
       </c>
-      <c r="F166" s="9" t="s">
+      <c r="F166" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G166" s="6" t="s">
+      <c r="G166" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="167" spans="5:7">
-      <c r="E167" s="6"/>
-      <c r="F167" s="9" t="s">
+      <c r="F167" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G167" s="6" t="s">
+      <c r="G167" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="168" spans="5:7">
-      <c r="E168" s="6"/>
-      <c r="F168" s="9" t="s">
+      <c r="F168" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G168" s="7" t="s">
+      <c r="G168" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="169" spans="5:7">
-      <c r="E169" s="6"/>
-      <c r="F169" s="9" t="s">
+      <c r="F169" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G169" s="7" t="s">
+      <c r="G169" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="170" spans="5:7">
-      <c r="E170" s="6"/>
-      <c r="F170" s="9" t="s">
+      <c r="F170" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G170" s="6" t="s">
+      <c r="G170" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="171" spans="5:7">
-      <c r="E171" s="6">
+      <c r="E171">
         <v>26</v>
       </c>
-      <c r="F171" s="9" t="s">
+      <c r="F171" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G171" s="7" t="s">
+      <c r="G171" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="172" spans="5:7">
-      <c r="E172" s="6">
+      <c r="E172">
         <v>27</v>
       </c>
-      <c r="F172" s="9" t="s">
+      <c r="F172" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G172" s="7" t="s">
+      <c r="G172" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="173" spans="5:7">
-      <c r="E173" s="6">
+      <c r="E173">
         <v>28</v>
       </c>
-      <c r="F173" s="9" t="s">
+      <c r="F173" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G173" s="6" t="s">
+      <c r="G173" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="174" spans="5:7">
-      <c r="E174" s="6"/>
-      <c r="F174" s="9" t="s">
+      <c r="F174" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G174" s="6" t="s">
+      <c r="G174" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="175" spans="5:7">
-      <c r="E175" s="6"/>
-      <c r="F175" s="9" t="s">
+      <c r="F175" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G175" s="6" t="s">
+      <c r="G175" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="176" spans="5:7">
-      <c r="E176" s="6"/>
-      <c r="F176" s="9" t="s">
+      <c r="F176" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G176" s="6" t="s">
+      <c r="G176" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="177" spans="6:10">
-      <c r="F177" s="9" t="s">
+      <c r="F177" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G177" s="6" t="s">
+      <c r="G177" t="s">
         <v>103</v>
       </c>
-      <c r="H177" s="6"/>
     </row>
     <row r="178" spans="6:10">
-      <c r="F178" s="9" t="s">
+      <c r="F178" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G178" s="7" t="s">
+      <c r="G178" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H178" s="6"/>
     </row>
     <row r="179" spans="6:10">
-      <c r="F179" s="9" t="s">
+      <c r="F179" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G179" s="7" t="s">
+      <c r="G179" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H179" s="6"/>
     </row>
     <row r="180" spans="6:10">
-      <c r="F180" s="9" t="s">
+      <c r="F180" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G180" s="7" t="s">
+      <c r="G180" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H180" s="6"/>
     </row>
     <row r="181" spans="6:10">
-      <c r="F181" s="9" t="s">
+      <c r="F181" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G181" s="6" t="s">
+      <c r="G181" t="s">
         <v>103</v>
       </c>
-      <c r="H181" s="6"/>
     </row>
     <row r="182" spans="6:10">
-      <c r="F182" s="9" t="s">
+      <c r="F182" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G182" s="6" t="s">
+      <c r="G182" t="s">
         <v>103</v>
       </c>
-      <c r="H182" s="6"/>
     </row>
     <row r="183" spans="6:10">
-      <c r="F183" s="9" t="s">
+      <c r="F183" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G183" s="6" t="s">
+      <c r="G183" t="s">
         <v>103</v>
       </c>
-      <c r="H183" s="6"/>
     </row>
     <row r="184" spans="6:10">
-      <c r="F184" s="9" t="s">
+      <c r="F184" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G184" s="6" t="s">
+      <c r="G184" t="s">
         <v>103</v>
       </c>
-      <c r="H184" s="6"/>
     </row>
     <row r="185" spans="6:10">
-      <c r="F185" s="9" t="s">
+      <c r="F185" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G185" s="6" t="s">
+      <c r="G185" t="s">
         <v>103</v>
       </c>
-      <c r="H185" s="6"/>
     </row>
     <row r="186" spans="6:10">
-      <c r="F186" s="9" t="s">
+      <c r="F186" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G186" s="6" t="s">
+      <c r="G186" t="s">
         <v>103</v>
       </c>
-      <c r="H186" s="6"/>
     </row>
     <row r="187" spans="6:10">
-      <c r="F187" s="9" t="s">
+      <c r="F187" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G187" s="6" t="s">
+      <c r="G187" t="s">
         <v>103</v>
       </c>
-      <c r="H187" s="6"/>
     </row>
     <row r="188" spans="6:10">
-      <c r="F188" s="9" t="s">
+      <c r="F188" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G188" s="6" t="s">
+      <c r="G188" t="s">
         <v>103</v>
       </c>
-      <c r="H188" s="6"/>
     </row>
     <row r="189" spans="6:10">
-      <c r="F189" s="6"/>
-      <c r="G189" s="10">
+      <c r="F189"/>
+      <c r="G189" s="5">
         <f>COUNTIF(G2:G188,"○")/COUNTA(G2:G188)</f>
         <v>0.40641711229946526</v>
       </c>
-      <c r="H189" s="6"/>
-      <c r="J189" s="10">
+      <c r="J189" s="5">
         <f>COUNTIF(J2:J188,"○")/COUNTA(J2:J188)</f>
-        <v>0.46153846153846156</v>
+        <v>0.38709677419354838</v>
       </c>
     </row>
   </sheetData>
@@ -4904,675 +4854,442 @@
       </c>
     </row>
     <row r="122" spans="2:6">
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6">
+      <c r="D122">
         <v>15</v>
       </c>
-      <c r="E122" s="6">
-        <v>1</v>
-      </c>
-      <c r="F122" s="9" t="s">
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="123" spans="2:6">
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6">
-        <v>2</v>
-      </c>
-      <c r="F123" s="9" t="s">
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" s="3" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="6">
-        <v>3</v>
-      </c>
-      <c r="F124" s="9" t="s">
+      <c r="E124">
+        <v>3</v>
+      </c>
+      <c r="F124" s="3" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="125" spans="2:6">
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6">
-        <v>4</v>
-      </c>
-      <c r="F125" s="9" t="s">
+      <c r="E125">
+        <v>4</v>
+      </c>
+      <c r="F125" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="126" spans="2:6">
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6">
+      <c r="E126">
         <v>5</v>
       </c>
-      <c r="F126" s="9">
+      <c r="F126" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="2:6">
-      <c r="B127" s="6">
-        <v>2</v>
-      </c>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6">
-        <v>1</v>
-      </c>
-      <c r="F127" s="9" t="s">
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="128" spans="2:6">
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6">
-        <v>2</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="2:6">
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6">
-        <v>3</v>
-      </c>
-      <c r="F129" s="9">
+      <c r="E128">
+        <v>2</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="5:6">
+      <c r="E129">
+        <v>3</v>
+      </c>
+      <c r="F129" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="6">
-        <v>4</v>
-      </c>
-      <c r="F130" s="9" t="s">
+    <row r="130" spans="5:6">
+      <c r="E130">
+        <v>4</v>
+      </c>
+      <c r="F130" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6">
+    <row r="131" spans="5:6">
+      <c r="E131">
         <v>5</v>
       </c>
-      <c r="F131" s="9" t="s">
+      <c r="F131" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="6">
+    <row r="132" spans="5:6">
+      <c r="E132">
         <v>6</v>
       </c>
-      <c r="F132" s="9" t="s">
+      <c r="F132" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6">
+    <row r="133" spans="5:6">
+      <c r="E133">
         <v>7</v>
       </c>
-      <c r="F133" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="2:6">
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6">
+      <c r="F133" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="5:6">
+      <c r="E134">
         <v>8</v>
       </c>
-      <c r="F134" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6">
+      <c r="F134" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="5:6">
+      <c r="E135">
         <v>9</v>
       </c>
-      <c r="F135" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6">
+      <c r="F135" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="5:6">
+      <c r="E136">
         <v>10</v>
       </c>
-      <c r="F136" s="9" t="s">
+      <c r="F136" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6">
+    <row r="137" spans="5:6">
+      <c r="E137">
         <v>11</v>
       </c>
-      <c r="F137" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6">
+      <c r="F137" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="5:6">
+      <c r="E138">
         <v>12</v>
       </c>
-      <c r="F138" s="9" t="s">
+      <c r="F138" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="9" t="s">
+    <row r="139" spans="5:6">
+      <c r="F139" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="9" t="s">
+    <row r="140" spans="5:6">
+      <c r="F140" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="9" t="s">
+    <row r="141" spans="5:6">
+      <c r="F141" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="142" spans="2:6">
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="9" t="s">
+    <row r="142" spans="5:6">
+      <c r="F142" s="3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="9" t="s">
+    <row r="143" spans="5:6">
+      <c r="F143" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6">
+    <row r="144" spans="5:6">
+      <c r="E144">
         <v>13</v>
       </c>
-      <c r="F144" s="9" t="s">
+      <c r="F144" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="145" spans="2:6">
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6">
-        <v>14</v>
-      </c>
-      <c r="F145" s="9" t="s">
+    <row r="145" spans="5:6">
+      <c r="E145">
+        <v>14</v>
+      </c>
+      <c r="F145" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="9" t="s">
+    <row r="146" spans="5:6">
+      <c r="F146" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="9" t="s">
+    <row r="147" spans="5:6">
+      <c r="F147" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="9" t="s">
+    <row r="148" spans="5:6">
+      <c r="F148" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="9" t="s">
+    <row r="149" spans="5:6">
+      <c r="F149" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6">
+    <row r="150" spans="5:6">
+      <c r="E150">
         <v>15</v>
       </c>
-      <c r="F150" s="9" t="s">
+      <c r="F150" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="151" spans="2:6">
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="9" t="s">
+    <row r="151" spans="5:6">
+      <c r="F151" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="9" t="s">
+    <row r="152" spans="5:6">
+      <c r="F152" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="153" spans="2:6">
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="9" t="s">
+    <row r="153" spans="5:6">
+      <c r="F153" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="154" spans="2:6">
-      <c r="B154" s="6"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="9" t="s">
+    <row r="154" spans="5:6">
+      <c r="F154" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="6"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="9" t="s">
+    <row r="155" spans="5:6">
+      <c r="F155" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="156" spans="2:6">
-      <c r="B156" s="6"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="9" t="s">
+    <row r="156" spans="5:6">
+      <c r="F156" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="157" spans="2:6">
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="6">
+    <row r="157" spans="5:6">
+      <c r="E157">
         <v>16</v>
       </c>
-      <c r="F157" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6">
-      <c r="B158" s="6"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="6">
+      <c r="F157" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="5:6">
+      <c r="E158">
         <v>17</v>
       </c>
-      <c r="F158" s="9" t="s">
+      <c r="F158" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="6"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="6">
+    <row r="159" spans="5:6">
+      <c r="E159">
         <v>18</v>
       </c>
-      <c r="F159" s="9" t="s">
+      <c r="F159" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="6">
+    <row r="160" spans="5:6">
+      <c r="E160">
         <v>19</v>
       </c>
-      <c r="F160" s="9" t="s">
+      <c r="F160" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="6"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="6">
+    <row r="161" spans="5:6">
+      <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="9" t="s">
+      <c r="F161" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="6"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="6">
+    <row r="162" spans="5:6">
+      <c r="E162">
         <v>21</v>
       </c>
-      <c r="F162" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="6"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="6">
+      <c r="F162" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="5:6">
+      <c r="E163">
         <v>22</v>
       </c>
-      <c r="F163" s="9" t="s">
+      <c r="F163" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="6"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="6">
+    <row r="164" spans="5:6">
+      <c r="E164">
         <v>23</v>
       </c>
-      <c r="F164" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="6">
+      <c r="F164" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="5:6">
+      <c r="E165">
         <v>24</v>
       </c>
-      <c r="F165" s="9" t="s">
+      <c r="F165" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="6">
+    <row r="166" spans="5:6">
+      <c r="E166">
         <v>25</v>
       </c>
-      <c r="F166" s="9" t="s">
+      <c r="F166" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="9" t="s">
+    <row r="167" spans="5:6">
+      <c r="F167" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="6"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="9" t="s">
+    <row r="168" spans="5:6">
+      <c r="F168" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="9" t="s">
+    <row r="169" spans="5:6">
+      <c r="F169" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="2:6">
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="9" t="s">
+    <row r="170" spans="5:6">
+      <c r="F170" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="171" spans="2:6">
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6">
+    <row r="171" spans="5:6">
+      <c r="E171">
         <v>26</v>
       </c>
-      <c r="F171" s="9" t="s">
+      <c r="F171" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6">
+    <row r="172" spans="5:6">
+      <c r="E172">
         <v>27</v>
       </c>
-      <c r="F172" s="9" t="s">
+      <c r="F172" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="173" spans="2:6">
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6">
+    <row r="173" spans="5:6">
+      <c r="E173">
         <v>28</v>
       </c>
-      <c r="F173" s="9" t="s">
+      <c r="F173" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="174" spans="2:6">
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="9" t="s">
+    <row r="174" spans="5:6">
+      <c r="F174" s="3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="175" spans="2:6">
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="9" t="s">
+    <row r="175" spans="5:6">
+      <c r="F175" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="9" t="s">
+    <row r="176" spans="5:6">
+      <c r="F176" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="9" t="s">
+    <row r="177" spans="6:6">
+      <c r="F177" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="178" spans="2:6">
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="9" t="s">
+    <row r="178" spans="6:6">
+      <c r="F178" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="179" spans="2:6">
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="9" t="s">
+    <row r="179" spans="6:6">
+      <c r="F179" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="9" t="s">
+    <row r="180" spans="6:6">
+      <c r="F180" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="181" spans="2:6">
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="9" t="s">
+    <row r="181" spans="6:6">
+      <c r="F181" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="182" spans="2:6">
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="9" t="s">
+    <row r="182" spans="6:6">
+      <c r="F182" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="183" spans="2:6">
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="9" t="s">
+    <row r="183" spans="6:6">
+      <c r="F183" s="3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="9" t="s">
+    <row r="184" spans="6:6">
+      <c r="F184" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="9" t="s">
+    <row r="185" spans="6:6">
+      <c r="F185" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="9" t="s">
+    <row r="186" spans="6:6">
+      <c r="F186" s="3" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="9" t="s">
+    <row r="187" spans="6:6">
+      <c r="F187" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="188" spans="2:6">
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="9" t="s">
+    <row r="188" spans="6:6">
+      <c r="F188" s="3" t="s">
         <v>39</v>
       </c>
     </row>

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B511E-91D6-4D94-9340-B5C906736529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3991D3-6C77-42A4-A06C-3D12CE650A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="176">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -1954,7 +1954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="4:8">
+    <row r="33" spans="4:11">
       <c r="D33">
         <v>5</v>
       </c>
@@ -1970,8 +1970,17 @@
       <c r="H33" s="2">
         <v>46163</v>
       </c>
-    </row>
-    <row r="34" spans="4:8">
+      <c r="I33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="34" spans="4:11">
       <c r="E34">
         <v>2</v>
       </c>
@@ -1981,8 +1990,14 @@
       <c r="G34" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="35" spans="4:8">
+      <c r="I34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="4:11">
       <c r="E35">
         <v>3</v>
       </c>
@@ -1992,8 +2007,14 @@
       <c r="G35" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="4:8">
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="4:11">
       <c r="E36">
         <v>4</v>
       </c>
@@ -2003,8 +2024,14 @@
       <c r="G36" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="4:8">
+      <c r="I36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="4:11">
       <c r="E37">
         <v>5</v>
       </c>
@@ -2014,8 +2041,14 @@
       <c r="G37" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="38" spans="4:8">
+      <c r="I37" t="s">
+        <v>0</v>
+      </c>
+      <c r="J37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="4:11">
       <c r="D38">
         <v>6</v>
       </c>
@@ -2029,7 +2062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="4:8">
+    <row r="39" spans="4:11">
       <c r="E39">
         <v>2</v>
       </c>
@@ -2040,7 +2073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="4:8">
+    <row r="40" spans="4:11">
       <c r="E40">
         <v>3</v>
       </c>
@@ -2051,7 +2084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="4:8">
+    <row r="41" spans="4:11">
       <c r="D41">
         <v>7</v>
       </c>
@@ -2068,7 +2101,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="42" spans="4:8">
+    <row r="42" spans="4:11">
       <c r="E42">
         <v>2</v>
       </c>
@@ -2079,7 +2112,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="4:8">
+    <row r="43" spans="4:11">
       <c r="F43" s="3">
         <v>1</v>
       </c>
@@ -2087,7 +2120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="4:8">
+    <row r="44" spans="4:11">
       <c r="F44" s="3">
         <v>3</v>
       </c>
@@ -2095,7 +2128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="4:8">
+    <row r="45" spans="4:11">
       <c r="E45">
         <v>3</v>
       </c>
@@ -2106,7 +2139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="4:8">
+    <row r="46" spans="4:11">
       <c r="E46">
         <v>4</v>
       </c>
@@ -2117,7 +2150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="4:8">
+    <row r="47" spans="4:11">
       <c r="E47">
         <v>5</v>
       </c>
@@ -2128,7 +2161,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="4:8">
+    <row r="48" spans="4:11">
       <c r="F48" s="3" t="s">
         <v>41</v>
       </c>
@@ -3570,7 +3603,7 @@
       </c>
       <c r="J189" s="5">
         <f>COUNTIF(J2:J188,"○")/COUNTA(J2:J188)</f>
-        <v>0.38709677419354838</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\ビジネスマネジャー\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\ビジネスマネジャー検定\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3991D3-6C77-42A4-A06C-3D12CE650A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F540684B-117A-4D1D-8068-F82D55F4A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="要点_問題" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="公式_解答_2" sheetId="7" r:id="rId8"/>
     <sheet name="公式_解答_3" sheetId="8" r:id="rId9"/>
     <sheet name="公式_分野別_解答" sheetId="10" r:id="rId10"/>
+    <sheet name="公式_Basic_問題" sheetId="11" r:id="rId11"/>
+    <sheet name="公式_Basic_解答" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,12 +42,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="151">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -199,6 +204,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>2 4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>2 5 8 10</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -223,6 +232,10 @@
     <rPh sb="4" eb="5">
       <t>ネン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>XRP</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -240,7 +253,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>XRP</t>
+    <t>KGI</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -248,10 +261,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>KGI</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2 5</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -260,64 +269,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2 4 6 10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2 3 4 5 7 9 10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ESG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スチュアートシップ・コード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>環境への配慮</t>
-    <rPh sb="0" eb="2">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ハイリョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>人権などを意味するソーシャル</t>
-    <rPh sb="0" eb="2">
-      <t>ジンケン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2 3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>項目</t>
-    <rPh sb="0" eb="2">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>値</t>
-    <rPh sb="0" eb="1">
-      <t>アタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2 4 5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>50 40</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -327,13 +278,6 @@
   </si>
   <si>
     <t>キャッシュフロー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>純利益</t>
-    <rPh sb="0" eb="3">
-      <t>ジュンリエキ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -361,6 +305,13 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>純利益</t>
+    <rPh sb="0" eb="3">
+      <t>ジュンリエキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>1 2 3 4 7</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -370,6 +321,10 @@
   </si>
   <si>
     <t>4 5 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -391,6 +346,459 @@
   </si>
   <si>
     <t>1 3 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 4 6 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3 4 5 7 9 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ESG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スチュアートシップ・コード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境への配慮</t>
+    <rPh sb="0" eb="2">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人権などを意味するソーシャル</t>
+    <rPh sb="0" eb="2">
+      <t>ジンケン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 4 5 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3 4 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3 4 5 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 4 5 6 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 5 6 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金融庁</t>
+    <rPh sb="0" eb="2">
+      <t>キンユウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京証券取引所</t>
+    <rPh sb="0" eb="2">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウケン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トリヒキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無視する</t>
+    <rPh sb="0" eb="2">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>順守しない</t>
+    <rPh sb="0" eb="2">
+      <t>ジュンシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モバイルワーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サテライトオフィス利用</t>
+    <rPh sb="9" eb="11">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>在宅勤務型テレワーク</t>
+    <rPh sb="0" eb="2">
+      <t>ザイタク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キンム</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テレワークに該当しない</t>
+    <rPh sb="6" eb="8">
+      <t>ガイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総務省</t>
+    <rPh sb="0" eb="3">
+      <t>ソウムショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パワハラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セクハラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数えられる</t>
+    <rPh sb="0" eb="1">
+      <t>カゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土下座・行き過ぎた謝罪の要求</t>
+    <rPh sb="0" eb="3">
+      <t>ドゲザ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シャザイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強いクレーム</t>
+    <rPh sb="0" eb="1">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>軽犯罪法</t>
+    <rPh sb="0" eb="4">
+      <t>ケイハンザイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 4 5 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハッキング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンピューターウイルス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機密性</t>
+    <rPh sb="0" eb="3">
+      <t>キミツセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完全性</t>
+    <rPh sb="0" eb="3">
+      <t>カンゼンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4 5 6 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4 6 8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境</t>
+    <rPh sb="0" eb="2">
+      <t>カンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人権</t>
+    <rPh sb="0" eb="2">
+      <t>ジンケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統治</t>
+    <rPh sb="0" eb="2">
+      <t>トウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタル社会の実現</t>
+    <rPh sb="4" eb="6">
+      <t>シャカイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジツゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>脱化石燃料などエネルギー変革</t>
+    <rPh sb="0" eb="1">
+      <t>ダツ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>カセキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ネンリョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIなど様々なデジタル規制</t>
+    <rPh sb="4" eb="6">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>倫理規制</t>
+    <rPh sb="0" eb="2">
+      <t>リンリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーパス設定</t>
+    <rPh sb="4" eb="6">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタルトランスフォーメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テレワーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミュニケーション改革</t>
+    <rPh sb="9" eb="11">
+      <t>カイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガバナンス改革</t>
+    <rPh sb="5" eb="7">
+      <t>カイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統合報告書</t>
+    <rPh sb="0" eb="2">
+      <t>トウゴウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3 5 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5 6 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金融庁</t>
+    <rPh sb="0" eb="3">
+      <t>キンユウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>順守する</t>
+    <rPh sb="0" eb="2">
+      <t>ジュンシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>厚生労働省</t>
+    <rPh sb="0" eb="2">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ロウドウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>身体・精神的な攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>シンタイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>セイシンテキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4 5 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>可用性</t>
+    <rPh sb="0" eb="3">
+      <t>カヨウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガバナンス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4 6 7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 3 4 6 7 8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スチュワードシップ・コード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統合報告書作成</t>
+    <rPh sb="0" eb="2">
+      <t>トウゴウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホウコクショ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 4 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4 6 9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 5 6 8 9 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 2 4 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3 4 5 9 10</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -445,6 +853,16 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>売上キャッシュフロー1900万円　仕入れキャッシュフロー1120万円</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>キャッシュフロー計算書</t>
     <rPh sb="8" eb="11">
       <t>ケイサンショ</t>
@@ -495,16 +913,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>売上キャッシュフロー1900万円　仕入れキャッシュフロー1120万円</t>
-    <rPh sb="0" eb="2">
-      <t>ウリアゲ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>税引前当期純利益</t>
     <rPh sb="0" eb="2">
       <t>ゼイビ</t>
@@ -533,38 +941,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3 4 5 6</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>4 5 6 7</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1 2 4 6</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 3 4 5 6</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 3 4 5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 3 5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 3 4 6</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 4 6 9 10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2 3 5</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -578,452 +958,6 @@
   </si>
   <si>
     <t>1 3 4 5 6</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 4 5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 3 4 5</t>
-  </si>
-  <si>
-    <t>✕</t>
-  </si>
-  <si>
-    <t>3 4 5 7</t>
-  </si>
-  <si>
-    <t>2 3 4 6</t>
-  </si>
-  <si>
-    <t>1 2 5 6</t>
-  </si>
-  <si>
-    <t>○</t>
-  </si>
-  <si>
-    <t>1 2</t>
-  </si>
-  <si>
-    <t>3 5</t>
-  </si>
-  <si>
-    <t>1 3 4</t>
-  </si>
-  <si>
-    <t>1 4 5 6 7</t>
-  </si>
-  <si>
-    <t>1 2 3 5 6 7</t>
-  </si>
-  <si>
-    <t>1 2 3</t>
-  </si>
-  <si>
-    <t>2 3 4 5</t>
-  </si>
-  <si>
-    <t>金融庁</t>
-    <rPh sb="0" eb="2">
-      <t>キンユウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>チョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>東京証券取引所</t>
-    <rPh sb="0" eb="2">
-      <t>トウキョウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショウケン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トリヒキ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コーポレートガバナンス・コード</t>
-  </si>
-  <si>
-    <t>無視する</t>
-    <rPh sb="0" eb="2">
-      <t>ムシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>順守しない</t>
-    <rPh sb="0" eb="2">
-      <t>ジュンシュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 3 4</t>
-  </si>
-  <si>
-    <t>モバイルワーク</t>
-  </si>
-  <si>
-    <t>サテライトオフィス利用</t>
-    <rPh sb="9" eb="11">
-      <t>リヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>在宅勤務型テレワーク</t>
-    <rPh sb="0" eb="2">
-      <t>ザイタク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キンム</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ガタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テレワークに該当しない</t>
-    <rPh sb="6" eb="8">
-      <t>ガイトウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>総務省</t>
-    <rPh sb="0" eb="3">
-      <t>ソウムショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パワハラ</t>
-  </si>
-  <si>
-    <t>セクハラ</t>
-  </si>
-  <si>
-    <t>数えられる</t>
-    <rPh sb="0" eb="1">
-      <t>カゾ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>土下座・行き過ぎた謝罪の要求</t>
-    <rPh sb="0" eb="3">
-      <t>ドゲザ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シャザイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヨウキュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>強いクレーム</t>
-    <rPh sb="0" eb="1">
-      <t>ツヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>軽犯罪法</t>
-    <rPh sb="0" eb="4">
-      <t>ケイハンザイホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 3</t>
-  </si>
-  <si>
-    <t>1 2 5</t>
-  </si>
-  <si>
-    <t>3 4 5 6</t>
-  </si>
-  <si>
-    <t>ハッキング</t>
-  </si>
-  <si>
-    <t>コンピューターウイルス</t>
-  </si>
-  <si>
-    <t>機密性</t>
-    <rPh sb="0" eb="3">
-      <t>キミツセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>完全性</t>
-    <rPh sb="0" eb="3">
-      <t>カンゼンセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 3 4 5</t>
-  </si>
-  <si>
-    <t>1 2 3 4 5 6 7</t>
-  </si>
-  <si>
-    <t>1 2 3 4 6 8</t>
-  </si>
-  <si>
-    <t>環境</t>
-    <rPh sb="0" eb="2">
-      <t>カンキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>人権</t>
-    <rPh sb="0" eb="2">
-      <t>ジンケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>統治</t>
-    <rPh sb="0" eb="2">
-      <t>トウチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デジタル社会の実現</t>
-    <rPh sb="4" eb="6">
-      <t>シャカイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジツゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>脱化石燃料などエネルギー変革</t>
-    <rPh sb="0" eb="1">
-      <t>ダツ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>カセキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ネンリョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヘンカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>AIなど様々なデジタル規制</t>
-    <rPh sb="4" eb="6">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>キセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>倫理規制</t>
-    <rPh sb="0" eb="2">
-      <t>リンリ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パーパス設定</t>
-    <rPh sb="4" eb="6">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デジタルトランスフォーメーション</t>
-  </si>
-  <si>
-    <t>統合報告書</t>
-    <rPh sb="0" eb="2">
-      <t>トウゴウ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ホウコクショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テレワーク</t>
-  </si>
-  <si>
-    <t>コミュニケーション改革</t>
-    <rPh sb="9" eb="11">
-      <t>カイカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ガバナンス改革</t>
-    <rPh sb="5" eb="7">
-      <t>カイカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2 5</t>
-  </si>
-  <si>
-    <t>4 6 9</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 3 4 5 7</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2 3 6</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 3 5 7</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>5 6 7</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>金融庁</t>
-    <rPh sb="0" eb="3">
-      <t>キンユウチョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>順守する</t>
-    <rPh sb="0" eb="2">
-      <t>ジュンシュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>モバイルワーク</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>厚生労働省</t>
-    <rPh sb="0" eb="2">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ロウドウショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パワハラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>セクハラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>身体・精神的な攻撃</t>
-    <rPh sb="0" eb="2">
-      <t>シンタイ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>セイシンテキ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ハッキング</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コンピューターウイルス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>可用性</t>
-    <rPh sb="0" eb="3">
-      <t>カヨウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ガバナンス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 3 4 6 7</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1 2 3 4 6 7 8</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スチュワードシップ・コード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>統合報告書作成</t>
-    <rPh sb="0" eb="2">
-      <t>トウゴウ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ホウコクショ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テレワーク</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デジタルトランスフォーメーション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3 5 6 8 9 10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3 4 5 9 10</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1381,14 +1315,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:K189"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="6" max="6" width="15" style="3" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.796875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.796875" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" customWidth="1"/>
+    <col min="9" max="9" width="8.796875" style="3"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11">
@@ -1414,7 +1349,7 @@
         <v>46139</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>4</v>
@@ -1451,7 +1386,7 @@
         <v>4</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>4</v>
@@ -1837,7 +1772,7 @@
         <v>4</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>4</v>
@@ -1854,7 +1789,7 @@
         <v>4</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>4</v>
@@ -1877,7 +1812,7 @@
         <v>46162</v>
       </c>
       <c r="I28" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>4</v>
@@ -1897,7 +1832,7 @@
         <v>4</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>4</v>
@@ -1914,7 +1849,7 @@
         <v>4</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>4</v>
@@ -1931,7 +1866,7 @@
         <v>4</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>4</v>
@@ -1954,7 +1889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="4:11">
+    <row r="33" spans="3:11">
       <c r="D33">
         <v>5</v>
       </c>
@@ -1980,7 +1915,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="34" spans="4:11">
+    <row r="34" spans="3:11">
       <c r="E34">
         <v>2</v>
       </c>
@@ -1997,7 +1932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="4:11">
+    <row r="35" spans="3:11">
       <c r="E35">
         <v>3</v>
       </c>
@@ -2014,7 +1949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="4:11">
+    <row r="36" spans="3:11">
       <c r="E36">
         <v>4</v>
       </c>
@@ -2031,7 +1966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="4:11">
+    <row r="37" spans="3:11">
       <c r="E37">
         <v>5</v>
       </c>
@@ -2048,7 +1983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="4:11">
+    <row r="38" spans="3:11">
       <c r="D38">
         <v>6</v>
       </c>
@@ -2056,13 +1991,13 @@
         <v>1</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="4:11">
+    <row r="39" spans="3:11">
       <c r="E39">
         <v>2</v>
       </c>
@@ -2073,18 +2008,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="4:11">
+    <row r="40" spans="3:11">
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="4:11">
+    <row r="41" spans="3:11">
+      <c r="C41">
+        <v>3</v>
+      </c>
       <c r="D41">
         <v>7</v>
       </c>
@@ -2092,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>4</v>
@@ -2101,7 +2039,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="42" spans="4:11">
+    <row r="42" spans="3:11">
       <c r="E42">
         <v>2</v>
       </c>
@@ -2112,7 +2050,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="4:11">
+    <row r="43" spans="3:11">
       <c r="F43" s="3">
         <v>1</v>
       </c>
@@ -2120,7 +2058,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="4:11">
+    <row r="44" spans="3:11">
       <c r="F44" s="3">
         <v>3</v>
       </c>
@@ -2128,18 +2066,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="4:11">
+    <row r="45" spans="3:11">
       <c r="E45">
         <v>3</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="4:11">
+    <row r="46" spans="3:11">
       <c r="E46">
         <v>4</v>
       </c>
@@ -2150,20 +2088,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="4:11">
+    <row r="47" spans="3:11">
       <c r="E47">
         <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="4:11">
+    <row r="48" spans="3:11">
       <c r="F48" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>12</v>
@@ -2171,7 +2109,7 @@
     </row>
     <row r="49" spans="4:8">
       <c r="F49" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>4</v>
@@ -2179,7 +2117,7 @@
     </row>
     <row r="50" spans="4:8">
       <c r="F50" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>12</v>
@@ -2187,7 +2125,7 @@
     </row>
     <row r="51" spans="4:8">
       <c r="F51" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>4</v>
@@ -2299,7 +2237,7 @@
     </row>
     <row r="62" spans="4:8">
       <c r="F62" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>4</v>
@@ -2321,7 +2259,7 @@
         <v>8</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>4</v>
@@ -2332,7 +2270,7 @@
         <v>9</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>12</v>
@@ -2343,7 +2281,7 @@
         <v>10</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>12</v>
@@ -2357,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>4</v>
@@ -2387,7 +2325,7 @@
         <v>4</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>4</v>
@@ -2398,7 +2336,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>4</v>
@@ -2411,7 +2349,7 @@
     </row>
     <row r="73" spans="4:7">
       <c r="F73" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>4</v>
@@ -2419,7 +2357,7 @@
     </row>
     <row r="74" spans="4:7">
       <c r="F74" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>4</v>
@@ -2427,7 +2365,7 @@
     </row>
     <row r="75" spans="4:7">
       <c r="F75" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>4</v>
@@ -2435,7 +2373,7 @@
     </row>
     <row r="76" spans="4:7">
       <c r="F76" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>4</v>
@@ -2457,7 +2395,7 @@
         <v>7</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>4</v>
@@ -2479,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>4</v>
@@ -2490,7 +2428,7 @@
         <v>10</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>4</v>
@@ -2504,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>4</v>
@@ -2518,7 +2456,7 @@
         <v>2</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>4</v>
@@ -2529,7 +2467,7 @@
         <v>3</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>4</v>
@@ -2576,7 +2514,7 @@
         <v>2</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>4</v>
@@ -2598,7 +2536,7 @@
         <v>4</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>12</v>
@@ -2645,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>4</v>
@@ -2700,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>12</v>
@@ -2711,7 +2649,7 @@
         <v>7</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>12</v>
@@ -2722,7 +2660,7 @@
         <v>8</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>4</v>
@@ -2776,100 +2714,46 @@
       <c r="E106">
         <v>1</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="107" spans="4:7">
       <c r="E107">
         <v>2</v>
       </c>
-      <c r="F107" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="108" spans="4:7">
       <c r="E108">
         <v>3</v>
       </c>
-      <c r="F108" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="109" spans="4:7">
       <c r="E109">
         <v>4</v>
       </c>
-      <c r="F109" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="110" spans="4:7">
       <c r="E110">
         <v>5</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="111" spans="4:7">
       <c r="E111">
         <v>6</v>
       </c>
-      <c r="F111" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="112" spans="4:7">
       <c r="E112">
         <v>7</v>
       </c>
-      <c r="F112" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="113" spans="2:8">
       <c r="E113">
         <v>8</v>
       </c>
-      <c r="F113" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="114" spans="2:8">
       <c r="E114">
         <v>9</v>
       </c>
-      <c r="F114" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="115" spans="2:8">
       <c r="D115">
@@ -2878,78 +2762,36 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="116" spans="2:8">
       <c r="E116">
         <v>2</v>
       </c>
-      <c r="F116" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="117" spans="2:8">
       <c r="E117">
         <v>3</v>
       </c>
-      <c r="F117" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="118" spans="2:8">
       <c r="E118">
         <v>4</v>
       </c>
-      <c r="F118" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="119" spans="2:8">
       <c r="E119">
         <v>5</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="120" spans="2:8">
       <c r="E120">
         <v>6</v>
       </c>
-      <c r="F120" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="121" spans="2:8">
       <c r="E121">
         <v>7</v>
       </c>
-      <c r="F121" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="122" spans="2:8">
       <c r="D122">
@@ -2959,10 +2801,10 @@
         <v>1</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="H122" s="2">
         <v>46172</v>
@@ -2973,10 +2815,10 @@
         <v>2</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="2:8">
@@ -2984,10 +2826,10 @@
         <v>3</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="2:8">
@@ -2995,10 +2837,10 @@
         <v>4</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="G125" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="2:8">
@@ -3006,10 +2848,10 @@
         <v>5</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="2:8">
@@ -3020,10 +2862,10 @@
         <v>1</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="G127" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="2:8">
@@ -3031,10 +2873,10 @@
         <v>2</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="G128" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="5:7">
@@ -3045,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="5:7">
@@ -3053,10 +2895,10 @@
         <v>4</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="5:7">
@@ -3064,10 +2906,10 @@
         <v>5</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="5:7">
@@ -3075,10 +2917,10 @@
         <v>6</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="5:7">
@@ -3086,10 +2928,10 @@
         <v>7</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="5:7">
@@ -3100,7 +2942,7 @@
         <v>2</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="5:7">
@@ -3111,7 +2953,7 @@
         <v>5</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="5:7">
@@ -3119,10 +2961,10 @@
         <v>10</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="5:7">
@@ -3133,7 +2975,7 @@
         <v>4</v>
       </c>
       <c r="G137" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" spans="5:7">
@@ -3141,50 +2983,50 @@
         <v>12</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="G138" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="5:7">
       <c r="F139" s="3" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="G139" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="5:7">
       <c r="F140" s="3" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="G140" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="5:7">
       <c r="F141" s="3" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="G141" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="5:7">
       <c r="F142" s="3" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="5:7">
       <c r="F143" s="3" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G143" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144" spans="5:7">
@@ -3192,10 +3034,10 @@
         <v>13</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="G144" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="5:7">
@@ -3203,42 +3045,42 @@
         <v>14</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G145" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="146" spans="5:7">
       <c r="F146" s="3" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="G146" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147" spans="5:7">
       <c r="F147" s="3" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G147" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="148" spans="5:7">
       <c r="F148" s="3" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="G148" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="149" spans="5:7">
       <c r="F149" s="3" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="G149" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150" spans="5:7">
@@ -3246,58 +3088,58 @@
         <v>15</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151" spans="5:7">
       <c r="F151" s="3" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="G151" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="152" spans="5:7">
       <c r="F152" s="3" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="G152" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="153" spans="5:7">
       <c r="F153" s="3" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="G153" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="154" spans="5:7">
       <c r="F154" s="3" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="G154" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="155" spans="5:7">
       <c r="F155" s="3" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="5:7">
       <c r="F156" s="3" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="G156" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157" spans="5:7">
@@ -3305,10 +3147,10 @@
         <v>16</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="5:7">
@@ -3316,10 +3158,10 @@
         <v>17</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="5:7">
@@ -3327,10 +3169,10 @@
         <v>18</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="5:7">
@@ -3338,10 +3180,10 @@
         <v>19</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="G160" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161" spans="5:7">
@@ -3349,10 +3191,10 @@
         <v>20</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="5:7">
@@ -3360,10 +3202,10 @@
         <v>21</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="5:7">
@@ -3371,10 +3213,10 @@
         <v>22</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="G163" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="164" spans="5:7">
@@ -3385,7 +3227,7 @@
         <v>6</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="5:7">
@@ -3393,10 +3235,10 @@
         <v>24</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="5:7">
@@ -3404,42 +3246,42 @@
         <v>25</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="G166" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="167" spans="5:7">
       <c r="F167" s="3" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="G167" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="168" spans="5:7">
       <c r="F168" s="3" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="5:7">
       <c r="F169" s="3" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="5:7">
       <c r="F170" s="3" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="G170" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171" spans="5:7">
@@ -3447,10 +3289,10 @@
         <v>26</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="5:7">
@@ -3458,10 +3300,10 @@
         <v>27</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="5:7">
@@ -3469,137 +3311,136 @@
         <v>28</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="G173" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="174" spans="5:7">
       <c r="F174" s="3" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="G174" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="175" spans="5:7">
       <c r="F175" s="3" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="G175" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="176" spans="5:7">
       <c r="F176" s="3" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="G176" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177" spans="6:10">
       <c r="F177" s="3" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="G177" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="178" spans="6:10">
       <c r="F178" s="3" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179" spans="6:10">
       <c r="F179" s="3" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180" spans="6:10">
       <c r="F180" s="3" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181" spans="6:10">
       <c r="F181" s="3" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="G181" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="182" spans="6:10">
       <c r="F182" s="3" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="G182" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="183" spans="6:10">
       <c r="F183" s="3" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="G183" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="184" spans="6:10">
       <c r="F184" s="3" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="G184" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="185" spans="6:10">
       <c r="F185" s="3" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="G185" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="186" spans="6:10">
       <c r="F186" s="3" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="G186" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="187" spans="6:10">
       <c r="F187" s="3" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="G187" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="188" spans="6:10">
       <c r="F188" s="3" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="G188" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="189" spans="6:10">
-      <c r="F189"/>
       <c r="G189" s="5">
         <f>COUNTIF(G2:G188,"○")/COUNTA(G2:G188)</f>
-        <v>0.40641711229946526</v>
+        <v>0.40935672514619881</v>
       </c>
       <c r="J189" s="5">
         <f>COUNTIF(J2:J188,"○")/COUNTA(J2:J188)</f>
@@ -3615,6 +3456,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63EE4CF6-5FAF-4DA5-8DC2-19CF25D39295}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="B2:C40"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
@@ -3910,6 +3752,192 @@
       </c>
       <c r="C40">
         <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCAAB6E-F3CE-4CD5-A253-8C4CE0F63326}">
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="D10" s="5">
+        <f>COUNTIF(D2:D9,"○")/COUNTA(D2:D9)</f>
+        <v>0.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BF38898-EF93-44E1-9B2E-FD4403C470F7}">
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3920,10 +3948,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012FFD73-E297-48A3-B6AA-5507307874C6}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:F188"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="6" max="6" width="8.83203125" style="3"/>
+    <col min="6" max="6" width="8.796875" style="3"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
@@ -4189,7 +4218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="4:6">
+    <row r="33" spans="3:6">
       <c r="D33">
         <v>5</v>
       </c>
@@ -4200,7 +4229,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="4:6">
+    <row r="34" spans="3:6">
       <c r="E34">
         <v>2</v>
       </c>
@@ -4208,7 +4237,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="4:6">
+    <row r="35" spans="3:6">
       <c r="E35">
         <v>3</v>
       </c>
@@ -4216,7 +4245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="4:6">
+    <row r="36" spans="3:6">
       <c r="E36">
         <v>4</v>
       </c>
@@ -4224,7 +4253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="4:6">
+    <row r="37" spans="3:6">
       <c r="E37">
         <v>5</v>
       </c>
@@ -4232,7 +4261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="4:6">
+    <row r="38" spans="3:6">
       <c r="D38">
         <v>6</v>
       </c>
@@ -4240,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="4:6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6">
       <c r="E39">
         <v>2</v>
       </c>
@@ -4251,15 +4280,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="4:6">
+    <row r="40" spans="3:6">
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="4:6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6">
+      <c r="C41">
+        <v>3</v>
+      </c>
       <c r="D41">
         <v>7</v>
       </c>
@@ -4270,7 +4302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="4:6">
+    <row r="42" spans="3:6">
       <c r="E42">
         <v>2</v>
       </c>
@@ -4278,25 +4310,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="4:6">
+    <row r="43" spans="3:6">
       <c r="F43" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="4:6">
+    <row r="44" spans="3:6">
       <c r="F44" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="4:6">
+    <row r="45" spans="3:6">
       <c r="E45">
         <v>3</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="4:6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6">
       <c r="E46">
         <v>4</v>
       </c>
@@ -4304,47 +4336,47 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="4:6">
+    <row r="47" spans="3:6">
       <c r="E47">
         <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="4:6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6">
       <c r="F48" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="4:6">
       <c r="F49" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="4:6">
       <c r="F50" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="4:6">
       <c r="F51" s="3" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="4:6">
       <c r="F52" s="3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="4:6">
       <c r="F53" s="3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="4:6">
       <c r="F54" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="4:6">
@@ -4395,7 +4427,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="4:6">
@@ -4403,12 +4435,12 @@
         <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="4:6">
       <c r="F62" s="3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="4:6">
@@ -4416,7 +4448,7 @@
         <v>7</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="4:6">
@@ -4424,7 +4456,7 @@
         <v>8</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="4:6">
@@ -4432,7 +4464,7 @@
         <v>9</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="4:6">
@@ -4440,7 +4472,7 @@
         <v>10</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="4:6">
@@ -4451,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="4:6">
@@ -4459,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="4:6">
@@ -4467,7 +4499,7 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="4:6">
@@ -4475,7 +4507,7 @@
         <v>4</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="4:6">
@@ -4483,32 +4515,32 @@
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="4:6">
       <c r="F72" s="3" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="4:6">
       <c r="F73" s="3" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74" spans="4:6">
       <c r="F74" s="3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="4:6">
       <c r="F75" s="3" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="4:6">
       <c r="F76" s="3" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="4:6">
@@ -4540,7 +4572,7 @@
         <v>9</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" spans="4:6">
@@ -4548,7 +4580,7 @@
         <v>10</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="4:6">
@@ -4567,7 +4599,7 @@
         <v>2</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84" spans="4:6">
@@ -4575,7 +4607,7 @@
         <v>3</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="4:6">
@@ -4591,7 +4623,7 @@
         <v>5</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="4:6">
@@ -4626,7 +4658,7 @@
         <v>4</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="4:6">
@@ -4650,7 +4682,7 @@
         <v>7</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="94" spans="4:6">
@@ -4677,7 +4709,7 @@
         <v>3</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="4:6">
@@ -4701,7 +4733,7 @@
         <v>6</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="4:6">
@@ -4709,7 +4741,7 @@
         <v>7</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="4:6">
@@ -4725,7 +4757,7 @@
         <v>9</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
     </row>
     <row r="103" spans="4:6">
@@ -4733,7 +4765,7 @@
         <v>10</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104" spans="4:6">
@@ -4760,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
     </row>
     <row r="107" spans="4:6">
@@ -4776,7 +4808,7 @@
         <v>3</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109" spans="4:6">
@@ -4784,7 +4816,7 @@
         <v>4</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
     </row>
     <row r="110" spans="4:6">
@@ -4792,7 +4824,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="111" spans="4:6">
@@ -4800,7 +4832,7 @@
         <v>6</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
     </row>
     <row r="112" spans="4:6">
@@ -4808,7 +4840,7 @@
         <v>7</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="113" spans="2:6">
@@ -4824,7 +4856,7 @@
         <v>9</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115" spans="2:6">
@@ -4835,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
     </row>
     <row r="116" spans="2:6">
@@ -4843,7 +4875,7 @@
         <v>2</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="2:6">
@@ -4894,7 +4926,7 @@
         <v>1</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="2:6">
@@ -4902,7 +4934,7 @@
         <v>2</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -4910,7 +4942,7 @@
         <v>3</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="125" spans="2:6">
@@ -4961,7 +4993,7 @@
         <v>4</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
     </row>
     <row r="131" spans="5:6">
@@ -4969,7 +5001,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="132" spans="5:6">
@@ -5025,32 +5057,32 @@
         <v>12</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139" spans="5:6">
       <c r="F139" s="3" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="140" spans="5:6">
       <c r="F140" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="141" spans="5:6">
       <c r="F141" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="5:6">
       <c r="F142" s="3" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
     </row>
     <row r="143" spans="5:6">
       <c r="F143" s="3" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
     </row>
     <row r="144" spans="5:6">
@@ -5058,7 +5090,7 @@
         <v>13</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145" spans="5:6">
@@ -5066,27 +5098,27 @@
         <v>14</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
     </row>
     <row r="146" spans="5:6">
       <c r="F146" s="3" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
     </row>
     <row r="147" spans="5:6">
       <c r="F147" s="3" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
     </row>
     <row r="148" spans="5:6">
       <c r="F148" s="3" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="5:6">
       <c r="F149" s="3" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
     </row>
     <row r="150" spans="5:6">
@@ -5094,37 +5126,37 @@
         <v>15</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
     </row>
     <row r="151" spans="5:6">
       <c r="F151" s="3" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
     </row>
     <row r="152" spans="5:6">
       <c r="F152" s="3" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153" spans="5:6">
       <c r="F153" s="3" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="154" spans="5:6">
       <c r="F154" s="3" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
     </row>
     <row r="155" spans="5:6">
       <c r="F155" s="3" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156" spans="5:6">
       <c r="F156" s="3" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
     </row>
     <row r="157" spans="5:6">
@@ -5140,7 +5172,7 @@
         <v>17</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="159" spans="5:6">
@@ -5148,7 +5180,7 @@
         <v>18</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="160" spans="5:6">
@@ -5156,7 +5188,7 @@
         <v>19</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="161" spans="5:6">
@@ -5196,7 +5228,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
     </row>
     <row r="166" spans="5:6">
@@ -5204,27 +5236,27 @@
         <v>25</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>164</v>
+        <v>96</v>
       </c>
     </row>
     <row r="167" spans="5:6">
       <c r="F167" s="3" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
     </row>
     <row r="168" spans="5:6">
       <c r="F168" s="3" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
     </row>
     <row r="169" spans="5:6">
       <c r="F169" s="3" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
     </row>
     <row r="170" spans="5:6">
       <c r="F170" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171" spans="5:6">
@@ -5232,7 +5264,7 @@
         <v>26</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>168</v>
+        <v>124</v>
       </c>
     </row>
     <row r="172" spans="5:6">
@@ -5240,7 +5272,7 @@
         <v>27</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="173" spans="5:6">
@@ -5248,82 +5280,82 @@
         <v>28</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
     </row>
     <row r="174" spans="5:6">
       <c r="F174" s="3" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="175" spans="5:6">
       <c r="F175" s="3" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
     </row>
     <row r="176" spans="5:6">
       <c r="F176" s="3" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
     </row>
     <row r="177" spans="6:6">
       <c r="F177" s="3" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178" spans="6:6">
       <c r="F178" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="179" spans="6:6">
       <c r="F179" s="3" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
     </row>
     <row r="180" spans="6:6">
       <c r="F180" s="3" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
     </row>
     <row r="181" spans="6:6">
       <c r="F181" s="3" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="182" spans="6:6">
       <c r="F182" s="3" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
     </row>
     <row r="183" spans="6:6">
       <c r="F183" s="3" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="184" spans="6:6">
       <c r="F184" s="3" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
     </row>
     <row r="185" spans="6:6">
       <c r="F185" s="3" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
     </row>
     <row r="186" spans="6:6">
       <c r="F186" s="3" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
     </row>
     <row r="187" spans="6:6">
       <c r="F187" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="188" spans="6:6">
       <c r="F188" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -5335,15 +5367,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2236A1BF-3EF1-45B2-8972-CB915DE2B880}">
-  <dimension ref="B2:H47"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="B2:N47"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="4" width="8.83203125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8">
+    <row r="2" spans="2:14">
       <c r="B2">
         <v>1</v>
       </c>
@@ -5365,8 +5402,26 @@
       <c r="H2" s="2">
         <v>46159</v>
       </c>
-    </row>
-    <row r="3" spans="2:8">
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46166</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
       <c r="B3">
         <v>2</v>
       </c>
@@ -5382,8 +5437,20 @@
       <c r="G3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="2:8">
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
       <c r="C4">
         <v>12</v>
       </c>
@@ -5396,8 +5463,20 @@
       <c r="G4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="2:8">
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
       <c r="C5">
         <v>8</v>
       </c>
@@ -5410,8 +5489,20 @@
       <c r="G5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="2:8">
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
       <c r="C6">
         <v>5</v>
       </c>
@@ -5424,8 +5515,20 @@
       <c r="G6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:8">
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7">
         <v>3</v>
       </c>
@@ -5441,8 +5544,20 @@
       <c r="G7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="2:8">
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="B8">
         <v>4</v>
       </c>
@@ -5458,8 +5573,20 @@
       <c r="G8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="2:8">
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9">
         <v>5</v>
       </c>
@@ -5475,8 +5602,20 @@
       <c r="G9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:8">
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10">
         <v>6</v>
       </c>
@@ -5492,8 +5631,20 @@
       <c r="G10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="2:8">
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>6</v>
+      </c>
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11">
         <v>7</v>
       </c>
@@ -5509,8 +5660,20 @@
       <c r="G11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="2:8">
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
       <c r="B12">
         <v>8</v>
       </c>
@@ -5526,8 +5689,20 @@
       <c r="G12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="2:8">
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
       <c r="B13">
         <v>9</v>
       </c>
@@ -5543,8 +5718,20 @@
       <c r="G13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="2:8">
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
       <c r="B14">
         <v>10</v>
       </c>
@@ -5560,8 +5747,20 @@
       <c r="G14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="2:8">
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15">
         <v>11</v>
       </c>
@@ -5577,8 +5776,20 @@
       <c r="G15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="2:8">
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
       <c r="B16">
         <v>12</v>
       </c>
@@ -5594,8 +5805,20 @@
       <c r="G16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
       <c r="B17">
         <v>13</v>
       </c>
@@ -5611,8 +5834,20 @@
       <c r="G17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
       <c r="B18">
         <v>14</v>
       </c>
@@ -5628,8 +5863,20 @@
       <c r="G18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
       <c r="B19">
         <v>15</v>
       </c>
@@ -5645,8 +5892,20 @@
       <c r="G19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
       <c r="B20">
         <v>16</v>
       </c>
@@ -5662,8 +5921,20 @@
       <c r="G20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
+      <c r="L20">
+        <v>4</v>
+      </c>
+      <c r="M20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
       <c r="B21">
         <v>17</v>
       </c>
@@ -5679,8 +5950,20 @@
       <c r="G21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
       <c r="B22">
         <v>18</v>
       </c>
@@ -5696,8 +5979,20 @@
       <c r="G22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
       <c r="B23">
         <v>19</v>
       </c>
@@ -5713,8 +6008,20 @@
       <c r="G23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>7</v>
+      </c>
+      <c r="M23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
       <c r="B24">
         <v>20</v>
       </c>
@@ -5730,8 +6037,20 @@
       <c r="G24" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="2:7">
+      <c r="I24">
+        <v>8</v>
+      </c>
+      <c r="J24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24">
+        <v>8</v>
+      </c>
+      <c r="M24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
       <c r="B25">
         <v>21</v>
       </c>
@@ -5747,8 +6066,20 @@
       <c r="G25" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="2:7">
+      <c r="I25">
+        <v>5</v>
+      </c>
+      <c r="J25" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25">
+        <v>5</v>
+      </c>
+      <c r="M25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
       <c r="B26">
         <v>22</v>
       </c>
@@ -5764,8 +6095,20 @@
       <c r="G26" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="2:7">
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
       <c r="D27" s="1" t="s">
         <v>4</v>
       </c>
@@ -5775,8 +6118,20 @@
       <c r="G27" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="2:7">
+      <c r="I27">
+        <v>9</v>
+      </c>
+      <c r="J27" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27">
+        <v>9</v>
+      </c>
+      <c r="M27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
       <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
@@ -5786,8 +6141,20 @@
       <c r="G28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="2:7">
+      <c r="I28">
+        <v>13</v>
+      </c>
+      <c r="J28" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28">
+        <v>13</v>
+      </c>
+      <c r="M28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
       <c r="B29">
         <v>23</v>
       </c>
@@ -5803,8 +6170,20 @@
       <c r="G29" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="2:7">
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29">
+        <v>4</v>
+      </c>
+      <c r="M29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
       <c r="B30">
         <v>24</v>
       </c>
@@ -5823,8 +6202,20 @@
       <c r="G30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="2:7">
+      <c r="I30">
+        <v>7</v>
+      </c>
+      <c r="J30" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30">
+        <v>5</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
       <c r="B31">
         <v>25</v>
       </c>
@@ -5840,8 +6231,20 @@
       <c r="G31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="2:7">
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
       <c r="B32">
         <v>26</v>
       </c>
@@ -5857,8 +6260,20 @@
       <c r="G32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="2:7">
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
       <c r="B33">
         <v>27</v>
       </c>
@@ -5874,8 +6289,20 @@
       <c r="G33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="2:7">
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13">
       <c r="B34">
         <v>28</v>
       </c>
@@ -5891,8 +6318,20 @@
       <c r="G34" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="2:7">
+      <c r="I34">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34">
+        <v>4</v>
+      </c>
+      <c r="M34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
       <c r="B35">
         <v>29</v>
       </c>
@@ -5908,8 +6347,20 @@
       <c r="G35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="2:7">
+      <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35">
+        <v>4</v>
+      </c>
+      <c r="M35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13">
       <c r="B36">
         <v>30</v>
       </c>
@@ -5925,8 +6376,20 @@
       <c r="G36" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="2:7">
+      <c r="I36">
+        <v>6</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L36">
+        <v>6</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
       <c r="B37">
         <v>31</v>
       </c>
@@ -5942,8 +6405,20 @@
       <c r="G37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="2:7">
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13">
       <c r="B38">
         <v>32</v>
       </c>
@@ -5959,8 +6434,20 @@
       <c r="G38" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="2:7">
+      <c r="I38">
+        <v>8</v>
+      </c>
+      <c r="J38" t="s">
+        <v>14</v>
+      </c>
+      <c r="L38">
+        <v>8</v>
+      </c>
+      <c r="M38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13">
       <c r="B39">
         <v>33</v>
       </c>
@@ -5976,8 +6463,20 @@
       <c r="G39" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="2:7">
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+      <c r="M39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13">
       <c r="B40">
         <v>34</v>
       </c>
@@ -5993,8 +6492,20 @@
       <c r="G40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="2:7">
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40">
+        <v>3</v>
+      </c>
+      <c r="M40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13">
       <c r="B41">
         <v>35</v>
       </c>
@@ -6010,8 +6521,20 @@
       <c r="G41" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:7">
+      <c r="I41">
+        <v>8</v>
+      </c>
+      <c r="J41" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41">
+        <v>8</v>
+      </c>
+      <c r="M41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13">
       <c r="B42">
         <v>36</v>
       </c>
@@ -6027,8 +6550,20 @@
       <c r="G42" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="43" spans="2:7">
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42">
+        <v>2</v>
+      </c>
+      <c r="M42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13">
       <c r="B43">
         <v>37</v>
       </c>
@@ -6044,8 +6579,20 @@
       <c r="G43" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:7">
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13">
       <c r="B44">
         <v>38</v>
       </c>
@@ -6061,8 +6608,20 @@
       <c r="G44" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="45" spans="2:7">
+      <c r="I44">
+        <v>4</v>
+      </c>
+      <c r="J44" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44">
+        <v>4</v>
+      </c>
+      <c r="M44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13">
       <c r="B45">
         <v>39</v>
       </c>
@@ -6078,8 +6637,20 @@
       <c r="G45" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="46" spans="2:7">
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45" t="s">
+        <v>14</v>
+      </c>
+      <c r="L45">
+        <v>4</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13">
       <c r="B46">
         <v>40</v>
       </c>
@@ -6095,8 +6666,20 @@
       <c r="G46" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="47" spans="2:7">
+      <c r="I46">
+        <v>4</v>
+      </c>
+      <c r="J46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L46">
+        <v>4</v>
+      </c>
+      <c r="M46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13">
       <c r="D47" s="5">
         <f>COUNTIF(D2:D46,"○")/COUNTA(D2:D46)</f>
         <v>0.57777777777777772</v>
@@ -6104,6 +6687,14 @@
       <c r="G47" s="5">
         <f>COUNTIF(G2:G46,"○")/COUNTA(G2:G46)</f>
         <v>0.75555555555555554</v>
+      </c>
+      <c r="J47" s="5">
+        <f>COUNTIF(J2:J46,"○")/COUNTA(J2:J46)</f>
+        <v>0.84444444444444444</v>
+      </c>
+      <c r="M47" s="5">
+        <f>COUNTIF(M2:M46,"○")/COUNTA(M2:M46)</f>
+        <v>0.91111111111111109</v>
       </c>
     </row>
   </sheetData>
@@ -6115,13 +6706,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93AD5C9-1ECA-423E-8B2D-666B3CE254BE}">
-  <dimension ref="B2:E44"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="B2:N44"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:14">
       <c r="B2">
         <v>1</v>
       </c>
@@ -6134,8 +6731,35 @@
       <c r="E2" s="2">
         <v>46152</v>
       </c>
-    </row>
-    <row r="3" spans="2:5">
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46165</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46172</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
       <c r="B3">
         <v>2</v>
       </c>
@@ -6145,8 +6769,26 @@
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="2:5">
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
       <c r="B4">
         <v>3</v>
       </c>
@@ -6156,8 +6798,26 @@
       <c r="D4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="2:5">
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4">
+        <v>6</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
       <c r="B5">
         <v>4</v>
       </c>
@@ -6167,8 +6827,26 @@
       <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="2:5">
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>5</v>
       </c>
@@ -6178,8 +6856,26 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:5">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7">
         <v>6</v>
       </c>
@@ -6189,16 +6885,52 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="2:5">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="2:5">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9">
         <v>7</v>
       </c>
@@ -6208,8 +6940,26 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:5">
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10">
         <v>8</v>
       </c>
@@ -6219,8 +6969,26 @@
       <c r="D10" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="2:5">
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11">
         <v>9</v>
       </c>
@@ -6230,8 +6998,26 @@
       <c r="D11" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
       <c r="B12">
         <v>10</v>
       </c>
@@ -6241,8 +7027,26 @@
       <c r="D12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="2:5">
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12">
+        <v>6</v>
+      </c>
+      <c r="M12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
       <c r="B13">
         <v>11</v>
       </c>
@@ -6252,8 +7056,26 @@
       <c r="D13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="2:5">
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13">
+        <v>5</v>
+      </c>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
       <c r="B14">
         <v>12</v>
       </c>
@@ -6263,8 +7085,26 @@
       <c r="D14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="2:5">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15">
         <v>13</v>
       </c>
@@ -6274,8 +7114,26 @@
       <c r="D15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="2:5">
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
       <c r="B16">
         <v>14</v>
       </c>
@@ -6285,8 +7143,26 @@
       <c r="D16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="2:4">
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <v>4</v>
+      </c>
+      <c r="M16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
       <c r="B17">
         <v>15</v>
       </c>
@@ -6296,8 +7172,26 @@
       <c r="D17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="2:4">
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
       <c r="B18">
         <v>16</v>
       </c>
@@ -6307,8 +7201,26 @@
       <c r="D18" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="2:4">
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
       <c r="B19">
         <v>17</v>
       </c>
@@ -6318,8 +7230,26 @@
       <c r="D19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="2:4">
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
+      <c r="L19">
+        <v>4</v>
+      </c>
+      <c r="M19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
       <c r="B20">
         <v>18</v>
       </c>
@@ -6329,8 +7259,26 @@
       <c r="D20" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="2:4">
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+      <c r="M20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
       <c r="B21">
         <v>19</v>
       </c>
@@ -6340,16 +7288,52 @@
       <c r="D21" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="2:4">
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
       <c r="C22">
         <v>5</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="2:4">
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>6</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
       <c r="B23">
         <v>20</v>
       </c>
@@ -6359,8 +7343,26 @@
       <c r="D23" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="2:4">
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
       <c r="B24">
         <v>21</v>
       </c>
@@ -6370,8 +7372,26 @@
       <c r="D24" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="2:4">
+      <c r="F24">
+        <v>11</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24">
+        <v>7</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <v>11</v>
+      </c>
+      <c r="M24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
       <c r="B25">
         <v>22</v>
       </c>
@@ -6381,8 +7401,26 @@
       <c r="D25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="2:4">
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
       <c r="B26">
         <v>23</v>
       </c>
@@ -6392,8 +7430,26 @@
       <c r="D26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="2:4">
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
       <c r="B27">
         <v>24</v>
       </c>
@@ -6403,8 +7459,26 @@
       <c r="D27" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="2:4">
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27">
+        <v>4</v>
+      </c>
+      <c r="M27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
       <c r="B28">
         <v>25</v>
       </c>
@@ -6414,8 +7488,26 @@
       <c r="D28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="2:4">
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28">
+        <v>4</v>
+      </c>
+      <c r="M28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
       <c r="B29">
         <v>26</v>
       </c>
@@ -6425,8 +7517,26 @@
       <c r="D29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="2:4">
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
       <c r="B30">
         <v>27</v>
       </c>
@@ -6436,8 +7546,26 @@
       <c r="D30" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="2:4">
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30">
+        <v>5</v>
+      </c>
+      <c r="M30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
       <c r="B31">
         <v>28</v>
       </c>
@@ -6447,8 +7575,26 @@
       <c r="D31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="2:4">
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
       <c r="B32">
         <v>29</v>
       </c>
@@ -6458,8 +7604,26 @@
       <c r="D32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="2:4">
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32">
+        <v>3</v>
+      </c>
+      <c r="M32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
       <c r="B33">
         <v>30</v>
       </c>
@@ -6469,8 +7633,26 @@
       <c r="D33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="2:4">
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33">
+        <v>3</v>
+      </c>
+      <c r="J33" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33">
+        <v>3</v>
+      </c>
+      <c r="M33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13">
       <c r="B34">
         <v>31</v>
       </c>
@@ -6480,8 +7662,26 @@
       <c r="D34" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="2:4">
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L34">
+        <v>3</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
       <c r="B35">
         <v>32</v>
       </c>
@@ -6491,8 +7691,26 @@
       <c r="D35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="2:4">
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35">
+        <v>4</v>
+      </c>
+      <c r="M35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13">
       <c r="B36">
         <v>33</v>
       </c>
@@ -6502,8 +7720,26 @@
       <c r="D36" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="2:4">
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L36">
+        <v>4</v>
+      </c>
+      <c r="M36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
       <c r="B37">
         <v>34</v>
       </c>
@@ -6513,8 +7749,26 @@
       <c r="D37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="2:4">
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L37">
+        <v>5</v>
+      </c>
+      <c r="M37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13">
       <c r="B38">
         <v>35</v>
       </c>
@@ -6524,8 +7778,26 @@
       <c r="D38" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="2:4">
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38">
+        <v>3</v>
+      </c>
+      <c r="M38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13">
       <c r="B39">
         <v>36</v>
       </c>
@@ -6535,8 +7807,26 @@
       <c r="D39" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="2:4">
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+      <c r="M39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13">
       <c r="B40">
         <v>37</v>
       </c>
@@ -6546,8 +7836,26 @@
       <c r="D40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="2:4">
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13">
       <c r="B41">
         <v>38</v>
       </c>
@@ -6557,8 +7865,26 @@
       <c r="D41" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="2:4">
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41">
+        <v>2</v>
+      </c>
+      <c r="M41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13">
       <c r="B42">
         <v>39</v>
       </c>
@@ -6568,8 +7894,26 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="43" spans="2:4">
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42">
+        <v>2</v>
+      </c>
+      <c r="M42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13">
       <c r="B43">
         <v>40</v>
       </c>
@@ -6579,11 +7923,41 @@
       <c r="D43" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:4">
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43">
+        <v>3</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13">
       <c r="D44" s="5">
         <f>COUNTIF(D2:D43,"○")/COUNTA(D2:D43)</f>
         <v>0.66666666666666663</v>
+      </c>
+      <c r="G44" s="5">
+        <f>COUNTIF(G2:G43,"○")/COUNTA(G2:G43)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J44" s="5">
+        <f>COUNTIF(J2:J43,"○")/COUNTA(J2:J43)</f>
+        <v>0.69047619047619047</v>
+      </c>
+      <c r="M44" s="5">
+        <f>COUNTIF(M2:M43,"○")/COUNTA(M2:M43)</f>
+        <v>0.90476190476190477</v>
       </c>
     </row>
   </sheetData>
@@ -6594,13 +7968,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE21359A-624F-4C05-BEF8-F84C6A18C92D}">
-  <dimension ref="B2:E48"/>
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="B2:K46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:11">
       <c r="B2">
         <v>1</v>
       </c>
@@ -6613,8 +7992,26 @@
       <c r="E2" s="2">
         <v>46158</v>
       </c>
-    </row>
-    <row r="3" spans="2:5">
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46165</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
       <c r="B3">
         <v>2</v>
       </c>
@@ -6624,8 +8021,20 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="2:5">
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
       <c r="B4">
         <v>3</v>
       </c>
@@ -6635,8 +8044,20 @@
       <c r="D4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="2:5">
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
       <c r="B5">
         <v>4</v>
       </c>
@@ -6646,8 +8067,20 @@
       <c r="D5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="2:5">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
       <c r="B6">
         <v>5</v>
       </c>
@@ -6657,8 +8090,20 @@
       <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="2:5">
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
       <c r="B7">
         <v>6</v>
       </c>
@@ -6668,8 +8113,20 @@
       <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="2:5">
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
       <c r="B8">
         <v>7</v>
       </c>
@@ -6679,8 +8136,20 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="2:5">
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
       <c r="B9">
         <v>8</v>
       </c>
@@ -6690,8 +8159,20 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:5">
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
       <c r="B10">
         <v>9</v>
       </c>
@@ -6701,8 +8182,20 @@
       <c r="D10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="2:5">
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
       <c r="B11">
         <v>10</v>
       </c>
@@ -6712,8 +8205,20 @@
       <c r="D11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
       <c r="B12">
         <v>11</v>
       </c>
@@ -6723,8 +8228,20 @@
       <c r="D12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="2:5">
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
       <c r="B13">
         <v>12</v>
       </c>
@@ -6734,8 +8251,20 @@
       <c r="D13" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="2:5">
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
       <c r="B14">
         <v>13</v>
       </c>
@@ -6745,8 +8274,20 @@
       <c r="D14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="2:5">
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
       <c r="B15">
         <v>14</v>
       </c>
@@ -6756,8 +8297,20 @@
       <c r="D15" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="2:5">
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
       <c r="B16">
         <v>15</v>
       </c>
@@ -6767,8 +8320,20 @@
       <c r="D16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="2:4">
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17">
         <v>16</v>
       </c>
@@ -6778,8 +8343,20 @@
       <c r="D17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="2:4">
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18">
         <v>17</v>
       </c>
@@ -6789,8 +8366,20 @@
       <c r="D18" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="2:4">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19">
         <v>18</v>
       </c>
@@ -6800,8 +8389,20 @@
       <c r="D19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="2:4">
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20">
         <v>19</v>
       </c>
@@ -6811,8 +8412,20 @@
       <c r="D20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="2:4">
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21">
         <v>20</v>
       </c>
@@ -6822,8 +8435,20 @@
       <c r="D21" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="2:4">
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22">
         <v>21</v>
       </c>
@@ -6833,8 +8458,20 @@
       <c r="D22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="2:4">
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23">
         <v>22</v>
       </c>
@@ -6844,8 +8481,20 @@
       <c r="D23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="2:4">
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
       <c r="B24">
         <v>23</v>
       </c>
@@ -6855,8 +8504,20 @@
       <c r="D24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="2:4">
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25">
         <v>24</v>
       </c>
@@ -6866,29 +8527,77 @@
       <c r="D25" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="2:4">
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25">
+        <v>3</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
       <c r="C26">
         <v>9</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="2:4">
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="2:4">
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
       <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="2:4">
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
       <c r="B29">
         <v>25</v>
       </c>
@@ -6898,8 +8607,20 @@
       <c r="D29" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="2:4">
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30">
         <v>26</v>
       </c>
@@ -6909,8 +8630,20 @@
       <c r="D30" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="2:4">
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
       <c r="B31">
         <v>27</v>
       </c>
@@ -6920,8 +8653,20 @@
       <c r="D31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="2:4">
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32">
         <v>28</v>
       </c>
@@ -6931,16 +8676,40 @@
       <c r="D32" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:4">
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="2:4">
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34">
         <v>29</v>
       </c>
@@ -6950,8 +8719,20 @@
       <c r="D34" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="2:4">
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35">
         <v>30</v>
       </c>
@@ -6961,75 +8742,183 @@
       <c r="D35" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="2:4">
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <v>6</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36">
         <v>31</v>
       </c>
       <c r="C36">
         <v>5</v>
       </c>
-      <c r="D36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
+      <c r="D36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37">
+        <v>32</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
       <c r="D37" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="D38" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37">
+        <v>6</v>
+      </c>
+      <c r="J37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38">
+        <v>33</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39">
+        <v>11</v>
+      </c>
+      <c r="J39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="2:4">
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
       <c r="B41">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C41">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D41" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="2:4">
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
+      <c r="J41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
+      <c r="D42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
       <c r="B43">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -7037,55 +8926,77 @@
       <c r="D43" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="44" spans="2:4">
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43">
+        <v>3</v>
+      </c>
+      <c r="J43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C44">
-        <v>4</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
       <c r="B45">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C45">
-        <v>3</v>
-      </c>
-      <c r="D45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46">
-        <v>39</v>
-      </c>
-      <c r="C46">
-        <v>2</v>
-      </c>
-      <c r="D46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47">
-        <v>40</v>
-      </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="D48" s="5">
-        <f>COUNTIF(D2:D47,"○")/COUNTA(D2:D47)</f>
-        <v>0.60869565217391308</v>
+        <v>2</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="D46" s="5">
+        <f>COUNTIF(D2:D45,"○")/COUNTA(D2:D45)</f>
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="G46" s="5">
+        <f>COUNTIF(G2:G45,"○")/COUNTA(G2:G45)</f>
+        <v>0.75</v>
+      </c>
+      <c r="J46" s="5">
+        <f>COUNTIF(J2:J45,"○")/COUNTA(J2:J45)</f>
+        <v>0.84090909090909094</v>
       </c>
     </row>
   </sheetData>
@@ -7096,13 +9007,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B9646A-C796-46EE-A75B-3B73C86BBB02}">
-  <dimension ref="B2:E41"/>
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="B2:K41"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:11">
       <c r="B2">
         <v>1</v>
       </c>
@@ -7115,8 +9031,26 @@
       <c r="E2" s="2">
         <v>46159</v>
       </c>
-    </row>
-    <row r="3" spans="2:5">
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46166</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
       <c r="B3">
         <v>2</v>
       </c>
@@ -7126,8 +9060,20 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="2:5">
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
       <c r="B4">
         <v>3</v>
       </c>
@@ -7137,8 +9083,20 @@
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:5">
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
       <c r="B5">
         <v>4</v>
       </c>
@@ -7148,8 +9106,20 @@
       <c r="D5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="2:5">
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
       <c r="B6">
         <v>5</v>
       </c>
@@ -7159,8 +9129,20 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:5">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
       <c r="B7">
         <v>6</v>
       </c>
@@ -7170,8 +9152,20 @@
       <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="2:5">
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
       <c r="B8">
         <v>7</v>
       </c>
@@ -7181,8 +9175,20 @@
       <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="2:5">
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
       <c r="B9">
         <v>8</v>
       </c>
@@ -7192,32 +9198,80 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:5">
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
       <c r="C10">
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="2:5">
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
       <c r="C12">
         <v>9</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="2:5">
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12">
+        <v>9</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
       <c r="B13">
         <v>9</v>
       </c>
@@ -7227,8 +9281,20 @@
       <c r="D13" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="2:5">
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
       <c r="B14">
         <v>10</v>
       </c>
@@ -7238,8 +9304,20 @@
       <c r="D14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="2:5">
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
       <c r="B15">
         <v>11</v>
       </c>
@@ -7249,8 +9327,20 @@
       <c r="D15" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="2:5">
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
       <c r="B16">
         <v>12</v>
       </c>
@@ -7260,8 +9350,20 @@
       <c r="D16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="2:4">
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17">
         <v>13</v>
       </c>
@@ -7271,8 +9373,20 @@
       <c r="D17" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="2:4">
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18">
         <v>14</v>
       </c>
@@ -7282,8 +9396,20 @@
       <c r="D18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="2:4">
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19">
         <v>15</v>
       </c>
@@ -7293,8 +9419,20 @@
       <c r="D19" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="2:4">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20">
         <v>16</v>
       </c>
@@ -7304,8 +9442,20 @@
       <c r="D20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="2:4">
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21">
         <v>17</v>
       </c>
@@ -7315,8 +9465,20 @@
       <c r="D21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="2:4">
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22">
         <v>18</v>
       </c>
@@ -7326,8 +9488,20 @@
       <c r="D22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="2:4">
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23">
         <v>19</v>
       </c>
@@ -7337,8 +9511,20 @@
       <c r="D23" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="2:4">
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
       <c r="B24">
         <v>20</v>
       </c>
@@ -7348,8 +9534,20 @@
       <c r="D24" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="2:4">
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25">
         <v>21</v>
       </c>
@@ -7359,32 +9557,80 @@
       <c r="D25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="2:4">
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25">
+        <v>8</v>
+      </c>
+      <c r="J25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="2:4">
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
       <c r="C27">
         <v>5</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="2:4">
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
       <c r="C28">
         <v>12</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="2:4">
+      <c r="F28">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28">
+        <v>12</v>
+      </c>
+      <c r="J28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
       <c r="B29">
         <v>22</v>
       </c>
@@ -7394,8 +9640,20 @@
       <c r="D29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="2:4">
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30">
         <v>23</v>
       </c>
@@ -7405,8 +9663,20 @@
       <c r="D30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="2:4">
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30">
+        <v>4</v>
+      </c>
+      <c r="J30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
       <c r="B31">
         <v>24</v>
       </c>
@@ -7416,8 +9686,20 @@
       <c r="D31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="2:4">
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32">
         <v>25</v>
       </c>
@@ -7427,8 +9709,20 @@
       <c r="D32" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:4">
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33">
         <v>26</v>
       </c>
@@ -7438,8 +9732,20 @@
       <c r="D33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="2:4">
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34">
         <v>27</v>
       </c>
@@ -7449,8 +9755,20 @@
       <c r="D34" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="2:4">
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35">
         <v>28</v>
       </c>
@@ -7460,8 +9778,20 @@
       <c r="D35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="2:4">
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36">
         <v>29</v>
       </c>
@@ -7471,8 +9801,20 @@
       <c r="D36" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:4">
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
       <c r="B37">
         <v>30</v>
       </c>
@@ -7482,8 +9824,20 @@
       <c r="D37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="2:4">
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38">
         <v>31</v>
       </c>
@@ -7493,8 +9847,20 @@
       <c r="D38" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="2:4">
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39">
         <v>32</v>
       </c>
@@ -7504,8 +9870,20 @@
       <c r="D39" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="2:4">
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40">
         <v>33</v>
       </c>
@@ -7515,11 +9893,31 @@
       <c r="D40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="2:4">
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
       <c r="D41" s="5">
         <f>COUNTIF(D2:D40,"○")/COUNTA(D2:D40)</f>
         <v>0.5641025641025641</v>
+      </c>
+      <c r="G41" s="5">
+        <f>COUNTIF(G2:G40,"○")/COUNTA(G2:G40)</f>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="J41" s="5">
+        <f>COUNTIF(J2:J40,"○")/COUNTA(J2:J40)</f>
+        <v>0.74358974358974361</v>
       </c>
     </row>
   </sheetData>
@@ -7530,10 +9928,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086BB6CF-01C1-4BF3-BA05-A563BD7AE114}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:C46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -7889,6 +10288,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A85306-807E-4BFC-AD03-5D9093B5FD87}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:C43"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
@@ -8230,7 +10630,8 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4308920F-4F49-4EA4-A901-EE38B83F4FDA}">
-  <dimension ref="B2:C47"/>
+  <sheetPr codeName="Sheet9"/>
+  <dimension ref="B2:C45"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:3">
@@ -8497,55 +10898,61 @@
       <c r="B36">
         <v>31</v>
       </c>
-      <c r="C36">
-        <v>2</v>
+      <c r="C36" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="2:3">
+      <c r="B37">
+        <v>32</v>
+      </c>
       <c r="C37">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="2:3">
+      <c r="B38">
+        <v>33</v>
+      </c>
       <c r="C38">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="B39">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="B40">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="B41">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C41">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="B42">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="B43">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -8553,33 +10960,17 @@
     </row>
     <row r="44" spans="2:3">
       <c r="B44">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="B45">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3">
-      <c r="B46">
-        <v>39</v>
-      </c>
-      <c r="C46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3">
-      <c r="B47">
-        <v>40</v>
-      </c>
-      <c r="C47">
         <v>4</v>
       </c>
     </row>

--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\ビジネスマネジャー検定\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F540684B-117A-4D1D-8068-F82D55F4A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD38FF8C-400B-46AA-B3D4-82044AA34452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="要点_問題" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,10 @@
     <sheet name="公式_問題_1" sheetId="3" r:id="rId3"/>
     <sheet name="公式_問題_2" sheetId="5" r:id="rId4"/>
     <sheet name="公式_問題_3" sheetId="6" r:id="rId5"/>
-    <sheet name="公式_分野別_問題" sheetId="9" r:id="rId6"/>
-    <sheet name="公式_解答_1" sheetId="4" r:id="rId7"/>
-    <sheet name="公式_解答_2" sheetId="7" r:id="rId8"/>
-    <sheet name="公式_解答_3" sheetId="8" r:id="rId9"/>
+    <sheet name="公式_解答_1" sheetId="4" r:id="rId6"/>
+    <sheet name="公式_解答_2" sheetId="7" r:id="rId7"/>
+    <sheet name="公式_解答_3" sheetId="8" r:id="rId8"/>
+    <sheet name="公式_分野別_問題" sheetId="9" r:id="rId9"/>
     <sheet name="公式_分野別_解答" sheetId="10" r:id="rId10"/>
     <sheet name="公式_Basic_問題" sheetId="11" r:id="rId11"/>
     <sheet name="公式_Basic_解答" sheetId="12" r:id="rId12"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="158">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -958,6 +958,46 @@
   </si>
   <si>
     <t>1 3 4 5 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 4 5 6 10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スチュアードシップ・コード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50 250</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>配当</t>
+    <rPh sb="0" eb="2">
+      <t>ハイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>債務</t>
+    <rPh sb="0" eb="2">
+      <t>サイム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当期純利益</t>
+    <rPh sb="0" eb="2">
+      <t>トウキ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ジュンリエキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5 6</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1996,6 +2036,15 @@
       <c r="G38" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I38" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2">
+        <v>46179</v>
+      </c>
     </row>
     <row r="39" spans="3:11">
       <c r="E39">
@@ -2007,6 +2056,12 @@
       <c r="G39" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I39" s="3">
+        <v>4</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="40" spans="3:11">
       <c r="E40">
@@ -2018,6 +2073,12 @@
       <c r="G40" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I40" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="41" spans="3:11">
       <c r="C41">
@@ -2038,6 +2099,13 @@
       <c r="H41" s="2">
         <v>46164</v>
       </c>
+      <c r="I41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="2"/>
     </row>
     <row r="42" spans="3:11">
       <c r="E42">
@@ -2049,6 +2117,12 @@
       <c r="G42" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I42" s="3">
+        <v>2</v>
+      </c>
+      <c r="J42" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="43" spans="3:11">
       <c r="F43" s="3">
@@ -2057,6 +2131,12 @@
       <c r="G43" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I43" s="3">
+        <v>1</v>
+      </c>
+      <c r="J43" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="44" spans="3:11">
       <c r="F44" s="3">
@@ -2065,6 +2145,12 @@
       <c r="G44" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I44" s="3">
+        <v>3</v>
+      </c>
+      <c r="J44" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="45" spans="3:11">
       <c r="E45">
@@ -2076,6 +2162,12 @@
       <c r="G45" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I45" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="46" spans="3:11">
       <c r="E46">
@@ -2085,6 +2177,12 @@
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2098,6 +2196,12 @@
       <c r="G47" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="48" spans="3:11">
       <c r="F48" s="3" t="s">
@@ -2106,24 +2210,42 @@
       <c r="G48" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="4:8">
+      <c r="I48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="4:11">
       <c r="F49" s="3" t="s">
         <v>43</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="4:8">
+      <c r="I49" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="4:11">
       <c r="F50" s="3" t="s">
         <v>44</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="51" spans="4:8">
+      <c r="I50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="4:11">
       <c r="F51" s="3" t="s">
         <v>45</v>
       </c>
@@ -2133,26 +2255,50 @@
       <c r="H51" s="2">
         <v>46167</v>
       </c>
-    </row>
-    <row r="52" spans="4:8">
+      <c r="I51" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="4:11">
       <c r="G52" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H52" s="2"/>
-    </row>
-    <row r="53" spans="4:8">
+      <c r="I52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="4:11">
       <c r="G53" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H53" s="2"/>
-    </row>
-    <row r="54" spans="4:8">
+      <c r="I53" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J53" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="4:11">
       <c r="G54" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H54" s="2"/>
-    </row>
-    <row r="55" spans="4:8">
+      <c r="I54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="4:11">
       <c r="E55">
         <v>6</v>
       </c>
@@ -2162,8 +2308,14 @@
       <c r="G55" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="4:8">
+      <c r="I55" s="3">
+        <v>3</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="4:11">
       <c r="D56">
         <v>8</v>
       </c>
@@ -2179,8 +2331,17 @@
       <c r="H56" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="57" spans="4:8">
+      <c r="I56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K56" s="2">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="57" spans="4:11">
       <c r="E57">
         <v>2</v>
       </c>
@@ -2190,8 +2351,14 @@
       <c r="G57" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="4:8">
+      <c r="I57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="4:11">
       <c r="E58">
         <v>3</v>
       </c>
@@ -2201,8 +2368,14 @@
       <c r="G58" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="4:8">
+      <c r="I58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J58" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="4:11">
       <c r="E59">
         <v>4</v>
       </c>
@@ -2212,8 +2385,14 @@
       <c r="G59" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="4:8">
+      <c r="I59" s="3">
+        <v>3</v>
+      </c>
+      <c r="J59" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="4:11">
       <c r="E60">
         <v>5</v>
       </c>
@@ -2223,8 +2402,14 @@
       <c r="G60" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="4:8">
+      <c r="I60" s="3">
+        <v>2</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="4:11">
       <c r="E61">
         <v>6</v>
       </c>
@@ -2234,16 +2419,28 @@
       <c r="G61" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="62" spans="4:8">
+      <c r="I61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="4:11">
       <c r="F62" s="3" t="s">
         <v>47</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="4:8">
+      <c r="I62" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="4:11">
       <c r="E63">
         <v>7</v>
       </c>
@@ -2253,8 +2450,14 @@
       <c r="G63" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="64" spans="4:8">
+      <c r="I63" s="3">
+        <v>4</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="4:11">
       <c r="E64">
         <v>8</v>
       </c>
@@ -2264,8 +2467,14 @@
       <c r="G64" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="65" spans="4:7">
+      <c r="I64" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="4:10">
       <c r="E65">
         <v>9</v>
       </c>
@@ -2275,8 +2484,14 @@
       <c r="G65" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="66" spans="4:7">
+      <c r="I65" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="4:10">
       <c r="E66">
         <v>10</v>
       </c>
@@ -2286,8 +2501,14 @@
       <c r="G66" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="4:7">
+      <c r="I66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="4:10">
       <c r="D67">
         <v>9</v>
       </c>
@@ -2300,16 +2521,28 @@
       <c r="G67" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="68" spans="4:7">
+      <c r="I67" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="4:10">
       <c r="E68">
         <v>2</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="69" spans="4:7">
+      <c r="I68" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="4:10">
       <c r="E69">
         <v>3</v>
       </c>
@@ -2319,8 +2552,14 @@
       <c r="G69" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="70" spans="4:7">
+      <c r="I69" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="4:10">
       <c r="E70">
         <v>4</v>
       </c>
@@ -2330,8 +2569,14 @@
       <c r="G70" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="4:7">
+      <c r="I70" s="3">
+        <v>20</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="4:10">
       <c r="E71">
         <v>5</v>
       </c>
@@ -2341,45 +2586,81 @@
       <c r="G71" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="4:7">
+      <c r="I71" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="4:10">
       <c r="G72" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="4:7">
+      <c r="I72" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J72" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="4:10">
       <c r="F73" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="74" spans="4:7">
+      <c r="I73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="4:10">
       <c r="F74" s="3" t="s">
         <v>54</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="75" spans="4:7">
+      <c r="I74" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="4:10">
       <c r="F75" s="3" t="s">
         <v>55</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="76" spans="4:7">
+      <c r="I75" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="4:10">
       <c r="F76" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="4:7">
+      <c r="I76" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="4:10">
       <c r="E77">
         <v>6</v>
       </c>
@@ -2389,8 +2670,14 @@
       <c r="G77" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="78" spans="4:7">
+      <c r="I77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J77" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="4:10">
       <c r="E78">
         <v>7</v>
       </c>
@@ -2400,8 +2687,14 @@
       <c r="G78" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="79" spans="4:7">
+      <c r="I78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="4:10">
       <c r="E79">
         <v>8</v>
       </c>
@@ -2411,8 +2704,14 @@
       <c r="G79" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="80" spans="4:7">
+      <c r="I79" s="3">
+        <v>2</v>
+      </c>
+      <c r="J79" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="4:10">
       <c r="E80">
         <v>9</v>
       </c>
@@ -2422,8 +2721,14 @@
       <c r="G80" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="81" spans="4:8">
+      <c r="I80" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="4:10">
       <c r="E81">
         <v>10</v>
       </c>
@@ -2433,8 +2738,14 @@
       <c r="G81" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="4:8">
+      <c r="I81" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="4:10">
       <c r="D82">
         <v>10</v>
       </c>
@@ -2451,7 +2762,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="83" spans="4:8">
+    <row r="83" spans="4:10">
       <c r="E83">
         <v>2</v>
       </c>
@@ -2462,7 +2773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="4:8">
+    <row r="84" spans="4:10">
       <c r="E84">
         <v>3</v>
       </c>
@@ -2473,7 +2784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="4:8">
+    <row r="85" spans="4:10">
       <c r="E85">
         <v>4</v>
       </c>
@@ -2484,7 +2795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="4:8">
+    <row r="86" spans="4:10">
       <c r="E86">
         <v>5</v>
       </c>
@@ -2495,7 +2806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="4:8">
+    <row r="87" spans="4:10">
       <c r="D87">
         <v>11</v>
       </c>
@@ -2509,7 +2820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="4:8">
+    <row r="88" spans="4:10">
       <c r="E88">
         <v>2</v>
       </c>
@@ -2520,7 +2831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="4:8">
+    <row r="89" spans="4:10">
       <c r="E89">
         <v>3</v>
       </c>
@@ -2531,7 +2842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="4:8">
+    <row r="90" spans="4:10">
       <c r="E90">
         <v>4</v>
       </c>
@@ -2542,7 +2853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="4:8">
+    <row r="91" spans="4:10">
       <c r="E91">
         <v>5</v>
       </c>
@@ -2553,7 +2864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="4:8">
+    <row r="92" spans="4:10">
       <c r="E92">
         <v>6</v>
       </c>
@@ -2564,7 +2875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="4:8">
+    <row r="93" spans="4:10">
       <c r="E93">
         <v>7</v>
       </c>
@@ -2575,7 +2886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="4:8">
+    <row r="94" spans="4:10">
       <c r="D94">
         <v>12</v>
       </c>
@@ -2589,7 +2900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="4:8">
+    <row r="95" spans="4:10">
       <c r="E95">
         <v>2</v>
       </c>
@@ -2600,7 +2911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="4:8">
+    <row r="96" spans="4:10">
       <c r="E96">
         <v>3</v>
       </c>
@@ -3444,7 +3755,7 @@
       </c>
       <c r="J189" s="5">
         <f>COUNTIF(J2:J188,"○")/COUNTA(J2:J188)</f>
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
     </row>
   </sheetData>
@@ -5368,7 +5679,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2236A1BF-3EF1-45B2-8972-CB915DE2B880}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B2:N47"/>
+  <dimension ref="B2:Q47"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
@@ -5377,10 +5688,12 @@
     <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
     <col min="9" max="10" width="0" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="0" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14">
+    <row r="2" spans="2:17">
       <c r="B2">
         <v>1</v>
       </c>
@@ -5420,8 +5733,17 @@
       <c r="N2" s="2">
         <v>46173</v>
       </c>
-    </row>
-    <row r="3" spans="2:14">
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17">
       <c r="B3">
         <v>2</v>
       </c>
@@ -5449,8 +5771,14 @@
       <c r="M3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="2:14">
+      <c r="O3">
+        <v>4</v>
+      </c>
+      <c r="P3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17">
       <c r="C4">
         <v>12</v>
       </c>
@@ -5475,8 +5803,14 @@
       <c r="M4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="2:14">
+      <c r="O4">
+        <v>12</v>
+      </c>
+      <c r="P4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17">
       <c r="C5">
         <v>8</v>
       </c>
@@ -5501,8 +5835,14 @@
       <c r="M5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="2:14">
+      <c r="O5">
+        <v>8</v>
+      </c>
+      <c r="P5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
       <c r="C6">
         <v>5</v>
       </c>
@@ -5527,8 +5867,14 @@
       <c r="M6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:14">
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17">
       <c r="B7">
         <v>3</v>
       </c>
@@ -5556,8 +5902,14 @@
       <c r="M7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="2:14">
+      <c r="O7">
+        <v>12</v>
+      </c>
+      <c r="P7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17">
       <c r="B8">
         <v>4</v>
       </c>
@@ -5585,8 +5937,14 @@
       <c r="M8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="2:14">
+      <c r="O8">
+        <v>7</v>
+      </c>
+      <c r="P8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17">
       <c r="B9">
         <v>5</v>
       </c>
@@ -5614,8 +5972,14 @@
       <c r="M9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:14">
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17">
       <c r="B10">
         <v>6</v>
       </c>
@@ -5643,8 +6007,14 @@
       <c r="M10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="2:14">
+      <c r="O10">
+        <v>6</v>
+      </c>
+      <c r="P10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17">
       <c r="B11">
         <v>7</v>
       </c>
@@ -5672,8 +6042,14 @@
       <c r="M11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="2:14">
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17">
       <c r="B12">
         <v>8</v>
       </c>
@@ -5701,8 +6077,14 @@
       <c r="M12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="2:14">
+      <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17">
       <c r="B13">
         <v>9</v>
       </c>
@@ -5730,8 +6112,14 @@
       <c r="M13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="2:14">
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17">
       <c r="B14">
         <v>10</v>
       </c>
@@ -5759,8 +6147,14 @@
       <c r="M14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="2:14">
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17">
       <c r="B15">
         <v>11</v>
       </c>
@@ -5788,8 +6182,14 @@
       <c r="M15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="2:14">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17">
       <c r="B16">
         <v>12</v>
       </c>
@@ -5817,8 +6217,14 @@
       <c r="M16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="2:13">
+      <c r="O16">
+        <v>4</v>
+      </c>
+      <c r="P16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16">
       <c r="B17">
         <v>13</v>
       </c>
@@ -5846,8 +6252,14 @@
       <c r="M17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="2:13">
+      <c r="O17">
+        <v>2</v>
+      </c>
+      <c r="P17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16">
       <c r="B18">
         <v>14</v>
       </c>
@@ -5875,8 +6287,14 @@
       <c r="M18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="2:13">
+      <c r="O18">
+        <v>2</v>
+      </c>
+      <c r="P18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16">
       <c r="B19">
         <v>15</v>
       </c>
@@ -5904,8 +6322,14 @@
       <c r="M19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="2:13">
+      <c r="O19">
+        <v>3</v>
+      </c>
+      <c r="P19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16">
       <c r="B20">
         <v>16</v>
       </c>
@@ -5933,8 +6357,14 @@
       <c r="M20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="2:13">
+      <c r="O20">
+        <v>4</v>
+      </c>
+      <c r="P20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16">
       <c r="B21">
         <v>17</v>
       </c>
@@ -5962,8 +6392,14 @@
       <c r="M21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="2:13">
+      <c r="O21">
+        <v>5</v>
+      </c>
+      <c r="P21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16">
       <c r="B22">
         <v>18</v>
       </c>
@@ -5991,8 +6427,14 @@
       <c r="M22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="2:13">
+      <c r="O22">
+        <v>2</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16">
       <c r="B23">
         <v>19</v>
       </c>
@@ -6020,8 +6462,14 @@
       <c r="M23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="2:13">
+      <c r="O23">
+        <v>7</v>
+      </c>
+      <c r="P23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16">
       <c r="B24">
         <v>20</v>
       </c>
@@ -6049,8 +6497,14 @@
       <c r="M24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="2:13">
+      <c r="O24">
+        <v>8</v>
+      </c>
+      <c r="P24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16">
       <c r="B25">
         <v>21</v>
       </c>
@@ -6078,8 +6532,14 @@
       <c r="M25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="2:13">
+      <c r="O25">
+        <v>5</v>
+      </c>
+      <c r="P25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16">
       <c r="B26">
         <v>22</v>
       </c>
@@ -6107,8 +6567,14 @@
       <c r="M26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="2:13">
+      <c r="O26">
+        <v>4</v>
+      </c>
+      <c r="P26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16">
       <c r="D27" s="1" t="s">
         <v>4</v>
       </c>
@@ -6130,8 +6596,14 @@
       <c r="M27" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="2:13">
+      <c r="O27">
+        <v>9</v>
+      </c>
+      <c r="P27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16">
       <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
@@ -6153,8 +6625,14 @@
       <c r="M28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="2:13">
+      <c r="O28">
+        <v>13</v>
+      </c>
+      <c r="P28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16">
       <c r="B29">
         <v>23</v>
       </c>
@@ -6182,8 +6660,14 @@
       <c r="M29" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="2:13">
+      <c r="O29">
+        <v>4</v>
+      </c>
+      <c r="P29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16">
       <c r="B30">
         <v>24</v>
       </c>
@@ -6214,8 +6698,14 @@
       <c r="M30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="2:13">
+      <c r="O30">
+        <v>7</v>
+      </c>
+      <c r="P30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16">
       <c r="B31">
         <v>25</v>
       </c>
@@ -6243,8 +6733,14 @@
       <c r="M31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="2:13">
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16">
       <c r="B32">
         <v>26</v>
       </c>
@@ -6272,8 +6768,14 @@
       <c r="M32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="2:13">
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="P32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16">
       <c r="B33">
         <v>27</v>
       </c>
@@ -6301,8 +6803,14 @@
       <c r="M33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="2:13">
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16">
       <c r="B34">
         <v>28</v>
       </c>
@@ -6330,8 +6838,14 @@
       <c r="M34" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="2:13">
+      <c r="O34">
+        <v>4</v>
+      </c>
+      <c r="P34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16">
       <c r="B35">
         <v>29</v>
       </c>
@@ -6359,8 +6873,14 @@
       <c r="M35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="2:13">
+      <c r="O35">
+        <v>4</v>
+      </c>
+      <c r="P35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16">
       <c r="B36">
         <v>30</v>
       </c>
@@ -6388,8 +6908,14 @@
       <c r="M36" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13">
+      <c r="O36">
+        <v>5</v>
+      </c>
+      <c r="P36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16">
       <c r="B37">
         <v>31</v>
       </c>
@@ -6417,8 +6943,14 @@
       <c r="M37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="2:13">
+      <c r="O37">
+        <v>2</v>
+      </c>
+      <c r="P37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16">
       <c r="B38">
         <v>32</v>
       </c>
@@ -6446,8 +6978,14 @@
       <c r="M38" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="2:13">
+      <c r="O38">
+        <v>7</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16">
       <c r="B39">
         <v>33</v>
       </c>
@@ -6475,8 +7013,14 @@
       <c r="M39" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="2:13">
+      <c r="O39">
+        <v>2</v>
+      </c>
+      <c r="P39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16">
       <c r="B40">
         <v>34</v>
       </c>
@@ -6504,8 +7048,14 @@
       <c r="M40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="2:13">
+      <c r="O40">
+        <v>3</v>
+      </c>
+      <c r="P40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16">
       <c r="B41">
         <v>35</v>
       </c>
@@ -6533,8 +7083,14 @@
       <c r="M41" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="2:13">
+      <c r="O41">
+        <v>8</v>
+      </c>
+      <c r="P41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16">
       <c r="B42">
         <v>36</v>
       </c>
@@ -6562,8 +7118,14 @@
       <c r="M42" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="43" spans="2:13">
+      <c r="O42">
+        <v>2</v>
+      </c>
+      <c r="P42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16">
       <c r="B43">
         <v>37</v>
       </c>
@@ -6591,8 +7153,14 @@
       <c r="M43" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="44" spans="2:13">
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16">
       <c r="B44">
         <v>38</v>
       </c>
@@ -6620,8 +7188,14 @@
       <c r="M44" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="45" spans="2:13">
+      <c r="O44">
+        <v>2</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16">
       <c r="B45">
         <v>39</v>
       </c>
@@ -6649,8 +7223,14 @@
       <c r="M45" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:13">
+      <c r="O45">
+        <v>2</v>
+      </c>
+      <c r="P45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16">
       <c r="B46">
         <v>40</v>
       </c>
@@ -6678,8 +7258,14 @@
       <c r="M46" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="47" spans="2:13">
+      <c r="O46">
+        <v>4</v>
+      </c>
+      <c r="P46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16">
       <c r="D47" s="5">
         <f>COUNTIF(D2:D46,"○")/COUNTA(D2:D46)</f>
         <v>0.57777777777777772</v>
@@ -6695,6 +7281,10 @@
       <c r="M47" s="5">
         <f>COUNTIF(M2:M46,"○")/COUNTA(M2:M46)</f>
         <v>0.91111111111111109</v>
+      </c>
+      <c r="P47" s="5">
+        <f>COUNTIF(P2:P46,"○")/COUNTA(P2:P46)</f>
+        <v>0.93333333333333335</v>
       </c>
     </row>
   </sheetData>
@@ -6714,7 +7304,8 @@
     <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
     <col min="6" max="7" width="8.796875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7969,17 +8560,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE21359A-624F-4C05-BEF8-F84C6A18C92D}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B2:K46"/>
+  <dimension ref="B2:N46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
     <col min="6" max="7" width="0" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11">
+    <row r="2" spans="2:14">
       <c r="B2">
         <v>1</v>
       </c>
@@ -8010,8 +8603,17 @@
       <c r="K2" s="2">
         <v>46172</v>
       </c>
-    </row>
-    <row r="3" spans="2:11">
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
       <c r="B3">
         <v>2</v>
       </c>
@@ -8033,8 +8635,14 @@
       <c r="J3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="2:11">
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
       <c r="B4">
         <v>3</v>
       </c>
@@ -8056,8 +8664,14 @@
       <c r="J4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="2:11">
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
       <c r="B5">
         <v>4</v>
       </c>
@@ -8079,8 +8693,14 @@
       <c r="J5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="2:11">
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>5</v>
       </c>
@@ -8102,8 +8722,14 @@
       <c r="J6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:11">
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7">
         <v>6</v>
       </c>
@@ -8125,8 +8751,14 @@
       <c r="J7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="2:11">
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="B8">
         <v>7</v>
       </c>
@@ -8148,8 +8780,14 @@
       <c r="J8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="2:11">
+      <c r="L8">
+        <v>4</v>
+      </c>
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9">
         <v>8</v>
       </c>
@@ -8171,8 +8809,14 @@
       <c r="J9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:11">
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10">
         <v>9</v>
       </c>
@@ -8194,8 +8838,14 @@
       <c r="J10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="2:11">
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11">
         <v>10</v>
       </c>
@@ -8217,8 +8867,14 @@
       <c r="J11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="2:11">
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
       <c r="B12">
         <v>11</v>
       </c>
@@ -8240,8 +8896,14 @@
       <c r="J12" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="2:11">
+      <c r="L12">
+        <v>3</v>
+      </c>
+      <c r="M12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
       <c r="B13">
         <v>12</v>
       </c>
@@ -8263,8 +8925,14 @@
       <c r="J13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="2:11">
+      <c r="L13">
+        <v>5</v>
+      </c>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
       <c r="B14">
         <v>13</v>
       </c>
@@ -8286,8 +8954,14 @@
       <c r="J14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="2:11">
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15">
         <v>14</v>
       </c>
@@ -8309,8 +8983,14 @@
       <c r="J15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="2:11">
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
       <c r="B16">
         <v>15</v>
       </c>
@@ -8332,8 +9012,14 @@
       <c r="J16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="2:10">
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
       <c r="B17">
         <v>16</v>
       </c>
@@ -8355,8 +9041,14 @@
       <c r="J17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="2:10">
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
       <c r="B18">
         <v>17</v>
       </c>
@@ -8378,8 +9070,14 @@
       <c r="J18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="2:10">
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
       <c r="B19">
         <v>18</v>
       </c>
@@ -8401,8 +9099,14 @@
       <c r="J19" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="2:10">
+      <c r="L19">
+        <v>6</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
       <c r="B20">
         <v>19</v>
       </c>
@@ -8424,8 +9128,14 @@
       <c r="J20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="2:10">
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
       <c r="B21">
         <v>20</v>
       </c>
@@ -8447,8 +9157,14 @@
       <c r="J21" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="2:10">
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
       <c r="B22">
         <v>21</v>
       </c>
@@ -8470,8 +9186,14 @@
       <c r="J22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="2:10">
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
       <c r="B23">
         <v>22</v>
       </c>
@@ -8493,8 +9215,14 @@
       <c r="J23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="2:10">
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
       <c r="B24">
         <v>23</v>
       </c>
@@ -8516,8 +9244,14 @@
       <c r="J24" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="2:10">
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
       <c r="B25">
         <v>24</v>
       </c>
@@ -8539,8 +9273,14 @@
       <c r="J25" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="2:10">
+      <c r="L25">
+        <v>7</v>
+      </c>
+      <c r="M25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
       <c r="C26">
         <v>9</v>
       </c>
@@ -8559,8 +9299,14 @@
       <c r="J26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="2:10">
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
       <c r="C27">
         <v>3</v>
       </c>
@@ -8579,8 +9325,14 @@
       <c r="J27" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="2:10">
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
       <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
@@ -8596,8 +9348,14 @@
       <c r="J28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="2:10">
+      <c r="L28">
+        <v>7</v>
+      </c>
+      <c r="M28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
       <c r="B29">
         <v>25</v>
       </c>
@@ -8619,8 +9377,14 @@
       <c r="J29" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="2:10">
+      <c r="L29">
+        <v>2</v>
+      </c>
+      <c r="M29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
       <c r="B30">
         <v>26</v>
       </c>
@@ -8642,8 +9406,14 @@
       <c r="J30" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="2:10">
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
       <c r="B31">
         <v>27</v>
       </c>
@@ -8665,8 +9435,14 @@
       <c r="J31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="2:10">
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
       <c r="B32">
         <v>28</v>
       </c>
@@ -8688,8 +9464,14 @@
       <c r="J32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="2:10">
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
       <c r="C33">
         <v>1</v>
       </c>
@@ -8708,8 +9490,14 @@
       <c r="J33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="2:10">
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13">
       <c r="B34">
         <v>29</v>
       </c>
@@ -8731,8 +9519,14 @@
       <c r="J34" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="2:10">
+      <c r="L34">
+        <v>4</v>
+      </c>
+      <c r="M34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
       <c r="B35">
         <v>30</v>
       </c>
@@ -8754,8 +9548,14 @@
       <c r="J35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="2:10">
+      <c r="L35">
+        <v>6</v>
+      </c>
+      <c r="M35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13">
       <c r="B36">
         <v>31</v>
       </c>
@@ -8777,8 +9577,14 @@
       <c r="J36" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="2:10">
+      <c r="L36" t="s">
+        <v>36</v>
+      </c>
+      <c r="M36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
       <c r="B37">
         <v>32</v>
       </c>
@@ -8800,8 +9606,14 @@
       <c r="J37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="2:10">
+      <c r="L37">
+        <v>6</v>
+      </c>
+      <c r="M37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13">
       <c r="B38">
         <v>33</v>
       </c>
@@ -8823,8 +9635,14 @@
       <c r="J38" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="2:10">
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13">
       <c r="B39">
         <v>34</v>
       </c>
@@ -8846,8 +9664,14 @@
       <c r="J39" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="2:10">
+      <c r="L39">
+        <v>11</v>
+      </c>
+      <c r="M39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13">
       <c r="B40">
         <v>35</v>
       </c>
@@ -8869,8 +9693,14 @@
       <c r="J40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="2:10">
+      <c r="L40">
+        <v>4</v>
+      </c>
+      <c r="M40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13">
       <c r="B41">
         <v>36</v>
       </c>
@@ -8892,8 +9722,14 @@
       <c r="J41" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="2:10">
+      <c r="L41">
+        <v>3</v>
+      </c>
+      <c r="M41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13">
       <c r="B42">
         <v>37</v>
       </c>
@@ -8915,8 +9751,14 @@
       <c r="J42" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="43" spans="2:10">
+      <c r="L42">
+        <v>3</v>
+      </c>
+      <c r="M42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13">
       <c r="B43">
         <v>38</v>
       </c>
@@ -8938,8 +9780,14 @@
       <c r="J43" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="44" spans="2:10">
+      <c r="L43">
+        <v>3</v>
+      </c>
+      <c r="M43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13">
       <c r="B44">
         <v>39</v>
       </c>
@@ -8961,8 +9809,14 @@
       <c r="J44" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="45" spans="2:10">
+      <c r="L44">
+        <v>2</v>
+      </c>
+      <c r="M44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13">
       <c r="B45">
         <v>40</v>
       </c>
@@ -8984,8 +9838,14 @@
       <c r="J45" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="46" spans="2:10">
+      <c r="L45">
+        <v>4</v>
+      </c>
+      <c r="M45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13">
       <c r="D46" s="5">
         <f>COUNTIF(D2:D45,"○")/COUNTA(D2:D45)</f>
         <v>0.61363636363636365</v>
@@ -8997,6 +9857,10 @@
       <c r="J46" s="5">
         <f>COUNTIF(J2:J45,"○")/COUNTA(J2:J45)</f>
         <v>0.84090909090909094</v>
+      </c>
+      <c r="M46" s="5">
+        <f>COUNTIF(M2:M45,"○")/COUNTA(M2:M45)</f>
+        <v>0.88636363636363635</v>
       </c>
     </row>
   </sheetData>
@@ -9006,927 +9870,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B9646A-C796-46EE-A75B-3B73C86BBB02}">
-  <sheetPr codeName="Sheet6"/>
-  <dimension ref="B2:K41"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="8.796875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:11">
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2">
-        <v>46159</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2">
-        <v>46166</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="2">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11">
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="C10">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10">
-        <v>5</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
-      <c r="J11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="C12">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12">
-        <v>9</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12">
-        <v>9</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13">
-        <v>9</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I13">
-        <v>5</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14">
-        <v>10</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15">
-        <v>11</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15">
-        <v>3</v>
-      </c>
-      <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15">
-        <v>3</v>
-      </c>
-      <c r="J15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16">
-        <v>12</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="J16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17">
-        <v>13</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18">
-        <v>14</v>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18">
-        <v>4</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19">
-        <v>15</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20">
-        <v>16</v>
-      </c>
-      <c r="C20">
-        <v>5</v>
-      </c>
-      <c r="D20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20">
-        <v>5</v>
-      </c>
-      <c r="J20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21">
-        <v>17</v>
-      </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21">
-        <v>3</v>
-      </c>
-      <c r="J21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22">
-        <v>18</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22">
-        <v>2</v>
-      </c>
-      <c r="J22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23">
-        <v>19</v>
-      </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24">
-        <v>20</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24">
-        <v>3</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="B25">
-        <v>21</v>
-      </c>
-      <c r="C25">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25">
-        <v>8</v>
-      </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25">
-        <v>8</v>
-      </c>
-      <c r="J25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26">
-        <v>2</v>
-      </c>
-      <c r="J26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="C27">
-        <v>5</v>
-      </c>
-      <c r="D27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27">
-        <v>5</v>
-      </c>
-      <c r="G27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27">
-        <v>5</v>
-      </c>
-      <c r="J27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="C28">
-        <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28">
-        <v>12</v>
-      </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28">
-        <v>12</v>
-      </c>
-      <c r="J28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29">
-        <v>22</v>
-      </c>
-      <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30">
-        <v>23</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30">
-        <v>4</v>
-      </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30">
-        <v>4</v>
-      </c>
-      <c r="J30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10">
-      <c r="B31">
-        <v>24</v>
-      </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31">
-        <v>3</v>
-      </c>
-      <c r="G31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31">
-        <v>3</v>
-      </c>
-      <c r="J31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10">
-      <c r="B32">
-        <v>25</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
-      <c r="B33">
-        <v>26</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="J33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10">
-      <c r="B34">
-        <v>27</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34">
-        <v>2</v>
-      </c>
-      <c r="J34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10">
-      <c r="B35">
-        <v>28</v>
-      </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35">
-        <v>3</v>
-      </c>
-      <c r="G35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35">
-        <v>3</v>
-      </c>
-      <c r="J35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
-      <c r="B36">
-        <v>29</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36">
-        <v>3</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36">
-        <v>3</v>
-      </c>
-      <c r="J36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10">
-      <c r="B37">
-        <v>30</v>
-      </c>
-      <c r="C37">
-        <v>3</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="G37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37">
-        <v>3</v>
-      </c>
-      <c r="J37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10">
-      <c r="B38">
-        <v>31</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I38">
-        <v>3</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10">
-      <c r="B39">
-        <v>32</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39">
-        <v>3</v>
-      </c>
-      <c r="G39" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39">
-        <v>3</v>
-      </c>
-      <c r="J39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10">
-      <c r="B40">
-        <v>33</v>
-      </c>
-      <c r="C40">
-        <v>5</v>
-      </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40">
-        <v>5</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40">
-        <v>5</v>
-      </c>
-      <c r="J40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10">
-      <c r="D41" s="5">
-        <f>COUNTIF(D2:D40,"○")/COUNTA(D2:D40)</f>
-        <v>0.5641025641025641</v>
-      </c>
-      <c r="G41" s="5">
-        <f>COUNTIF(G2:G40,"○")/COUNTA(G2:G40)</f>
-        <v>0.76923076923076927</v>
-      </c>
-      <c r="J41" s="5">
-        <f>COUNTIF(J2:J40,"○")/COUNTA(J2:J40)</f>
-        <v>0.74358974358974361</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086BB6CF-01C1-4BF3-BA05-A563BD7AE114}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:C46"/>
@@ -10286,7 +10229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A85306-807E-4BFC-AD03-5D9093B5FD87}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:C43"/>
@@ -10628,7 +10571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4308920F-4F49-4EA4-A901-EE38B83F4FDA}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:C45"/>
@@ -10978,4 +10921,1168 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B9646A-C796-46EE-A75B-3B73C86BBB02}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="B2:N41"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="3" max="4" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46159</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46166</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46173</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>6</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9">
+        <v>11</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10">
+        <v>5</v>
+      </c>
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11">
+        <v>7</v>
+      </c>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12">
+        <v>9</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12">
+        <v>9</v>
+      </c>
+      <c r="M12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
+      <c r="L20">
+        <v>5</v>
+      </c>
+      <c r="M20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="M21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>14</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25">
+        <v>8</v>
+      </c>
+      <c r="J25" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25">
+        <v>8</v>
+      </c>
+      <c r="M25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="C28">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28">
+        <v>12</v>
+      </c>
+      <c r="J28" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28">
+        <v>12</v>
+      </c>
+      <c r="M28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29">
+        <v>22</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30">
+        <v>23</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30">
+        <v>4</v>
+      </c>
+      <c r="J30" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30">
+        <v>4</v>
+      </c>
+      <c r="M30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31">
+        <v>3</v>
+      </c>
+      <c r="M31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32">
+        <v>25</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
+      <c r="B33">
+        <v>26</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13">
+      <c r="B34">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
+      <c r="B35">
+        <v>28</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35">
+        <v>3</v>
+      </c>
+      <c r="M35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13">
+      <c r="B36">
+        <v>29</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36">
+        <v>3</v>
+      </c>
+      <c r="M36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
+      <c r="B37">
+        <v>30</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+      <c r="M37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13">
+      <c r="B38">
+        <v>31</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38">
+        <v>4</v>
+      </c>
+      <c r="M38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13">
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39">
+        <v>3</v>
+      </c>
+      <c r="M39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13">
+      <c r="B40">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>5</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40">
+        <v>5</v>
+      </c>
+      <c r="M40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13">
+      <c r="D41" s="5">
+        <f>COUNTIF(D2:D40,"○")/COUNTA(D2:D40)</f>
+        <v>0.5641025641025641</v>
+      </c>
+      <c r="G41" s="5">
+        <f>COUNTIF(G2:G40,"○")/COUNTA(G2:G40)</f>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="J41" s="5">
+        <f>COUNTIF(J2:J40,"○")/COUNTA(J2:J40)</f>
+        <v>0.74358974358974361</v>
+      </c>
+      <c r="M41" s="5">
+        <f>COUNTIF(M2:M40,"○")/COUNTA(M2:M40)</f>
+        <v>0.94871794871794868</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ビジネスマネジャー検定.xlsx
+++ b/ビジネスマネジャー検定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\ビジネスマネジャー検定\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD38FF8C-400B-46AA-B3D4-82044AA34452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480AB4EC-C310-4CA6-94A9-64CC1A693C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="158">
   <si>
     <t>1 2</t>
     <phoneticPr fontId="1"/>
@@ -2761,6 +2761,12 @@
       <c r="H82" s="2">
         <v>46169</v>
       </c>
+      <c r="I82" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="83" spans="4:10">
       <c r="E83">
@@ -2772,6 +2778,12 @@
       <c r="G83" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I83" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J83" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="84" spans="4:10">
       <c r="E84">
@@ -2783,6 +2795,12 @@
       <c r="G84" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="85" spans="4:10">
       <c r="E85">
@@ -2793,6 +2811,12 @@
       </c>
       <c r="G85" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J85" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="4:10">
@@ -2805,6 +2829,12 @@
       <c r="G86" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I86" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="87" spans="4:10">
       <c r="D87">
@@ -2819,6 +2849,12 @@
       <c r="G87" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I87" s="3">
+        <v>5</v>
+      </c>
+      <c r="J87" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="88" spans="4:10">
       <c r="E88">
@@ -2830,6 +2866,12 @@
       <c r="G88" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I88" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="89" spans="4:10">
       <c r="E89">
@@ -2841,6 +2883,12 @@
       <c r="G89" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I89" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J89" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="90" spans="4:10">
       <c r="E90">
@@ -2851,6 +2899,12 @@
       </c>
       <c r="G90" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J90" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="4:10">
@@ -2863,6 +2917,12 @@
       <c r="G91" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="92" spans="4:10">
       <c r="E92">
@@ -2874,6 +2934,12 @@
       <c r="G92" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I92" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J92" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="93" spans="4:10">
       <c r="E93">
@@ -2883,6 +2949,12 @@
         <v>2</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3755,7 +3827,7 @@
       </c>
       <c r="J189" s="5">
         <f>COUNTIF(J2:J188,"○")/COUNTA(J2:J188)</f>
-        <v>0.4375</v>
+        <v>0.45652173913043476</v>
       </c>
     </row>
   </sheetData>
